--- a/ARM Functions/Other Mechanics/Shop Sizes shop cro.xlsx
+++ b/ARM Functions/Other Mechanics/Shop Sizes shop cro.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\Other Mechanics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A97678B4-F9AA-45E8-8C7C-F31A7A906E76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AECE0AA8-AE67-4560-AF22-1F23C4657762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16457" yWindow="0" windowWidth="16457" windowHeight="17914" firstSheet="1" activeTab="2" xr2:uid="{F756E94B-0784-4072-B01E-8E7D98F4D78E}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18120" firstSheet="1" activeTab="2" xr2:uid="{F756E94B-0784-4072-B01E-8E7D98F4D78E}"/>
   </bookViews>
   <sheets>
     <sheet name="Table" sheetId="2" r:id="rId1"/>
@@ -23,7 +23,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Edited!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterate="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7815" uniqueCount="3946">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7869" uniqueCount="3965">
   <si>
     <t>Poké Ball</t>
   </si>
@@ -11904,6 +11904,63 @@
   </si>
   <si>
     <t>Ribombinite</t>
+  </si>
+  <si>
+    <t>Crabominite</t>
+  </si>
+  <si>
+    <t>Drampanite</t>
+  </si>
+  <si>
+    <t>Excadrite</t>
+  </si>
+  <si>
+    <t>Emboarite</t>
+  </si>
+  <si>
+    <t>Hawluchanite</t>
+  </si>
+  <si>
+    <t>Meowsticite</t>
+  </si>
+  <si>
+    <t>Starminite</t>
+  </si>
+  <si>
+    <t>Raichunite X</t>
+  </si>
+  <si>
+    <t>Raichunite Y</t>
+  </si>
+  <si>
+    <t>Squirtilium U</t>
+  </si>
+  <si>
+    <t>Dragalgite</t>
+  </si>
+  <si>
+    <t>Eelektrossite</t>
+  </si>
+  <si>
+    <t>Gumshoosinite</t>
+  </si>
+  <si>
+    <t>Malamarite</t>
+  </si>
+  <si>
+    <t>Pyroarite</t>
+  </si>
+  <si>
+    <t>Scolipite</t>
+  </si>
+  <si>
+    <t>Scraftinite</t>
+  </si>
+  <si>
+    <t>Staraptite</t>
+  </si>
+  <si>
+    <t>Barbaricite</t>
   </si>
 </sst>
 </file>
@@ -38453,14 +38510,14 @@
       </c>
       <c r="S33">
         <f>COUNTIF(Edited!D:D,"="&amp;'Table of addresses'!Q33)</f>
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="T33">
         <v>4</v>
       </c>
       <c r="U33">
         <f t="shared" si="2"/>
-        <v>280</v>
+        <v>424</v>
       </c>
     </row>
     <row r="34" spans="1:21">
@@ -39089,7 +39146,7 @@
       <c r="N44" s="4"/>
       <c r="U44">
         <f>SUM(U2:U43)</f>
-        <v>1086</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="45" spans="1:21">
@@ -39227,7 +39284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{480EC6E0-FD61-4408-8DFB-D1CC2117B0F2}">
-  <dimension ref="A1:N1047"/>
+  <dimension ref="A1:N1083"/>
   <sheetFormatPr defaultRowHeight="14.15"/>
   <cols>
     <col min="1" max="1" width="5.7109375" bestFit="1" customWidth="1"/>
@@ -40974,7 +41031,7 @@
       </c>
       <c r="J44">
         <f>COUNTIFS(D:D,"="&amp;I44)/2</f>
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="K44">
         <f>COUNTIFS(Table!F:F,"="&amp;I44)/2</f>
@@ -44435,7 +44492,7 @@
       </c>
       <c r="B224" s="4" t="str">
         <f>DEC2HEX(COUNTIF(D:D,"="&amp;C224)/2,2)</f>
-        <v>4D</v>
+        <v>5F</v>
       </c>
       <c r="C224" s="4" t="s">
         <v>2802</v>
@@ -53301,10 +53358,10 @@
       </c>
       <c r="B723" t="str">
         <f>_xlfn.XLOOKUP(C723,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>7B00</v>
+        <v>7D03</v>
       </c>
       <c r="C723" t="s">
-        <v>3852</v>
+        <v>3955</v>
       </c>
       <c r="D723" t="s">
         <v>2798</v>
@@ -54663,7 +54720,7 @@
     </row>
     <row r="804" spans="1:5">
       <c r="A804" t="str">
-        <f t="shared" ref="A804:A874" si="124">DEC2HEX(HEX2DEC(A803)+LEN(B803)/2,4)</f>
+        <f t="shared" ref="A804:A876" si="124">DEC2HEX(HEX2DEC(A803)+LEN(B803)/2,4)</f>
         <v>9DAA</v>
       </c>
       <c r="B804" t="str">
@@ -55694,7 +55751,7 @@
         <v>A01E</v>
       </c>
       <c r="B862" t="str">
-        <f t="shared" ref="B862:B864" si="152">RIGHT(DEC2HEX(C862,4),2)&amp;LEFT(DEC2HEX(C862,4),2)</f>
+        <f t="shared" ref="B862" si="152">RIGHT(DEC2HEX(C862,4),2)&amp;LEFT(DEC2HEX(C862,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C862">
@@ -55855,10 +55912,10 @@
       </c>
       <c r="B871" t="str">
         <f>_xlfn.XLOOKUP(C871,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>0203</v>
+        <v>8603</v>
       </c>
       <c r="C871" t="s">
-        <v>2264</v>
+        <v>3964</v>
       </c>
       <c r="D871" t="s">
         <v>2802</v>
@@ -55891,10 +55948,10 @@
       </c>
       <c r="B873" t="str">
         <f>_xlfn.XLOOKUP(C873,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>9502</v>
+        <v>0203</v>
       </c>
       <c r="C873" t="s">
-        <v>1949</v>
+        <v>2264</v>
       </c>
       <c r="D873" t="s">
         <v>2802</v>
@@ -55922,15 +55979,15 @@
     </row>
     <row r="875" spans="1:5">
       <c r="A875" t="str">
-        <f t="shared" ref="A875:A938" si="159">DEC2HEX(HEX2DEC(A874)+LEN(B874)/2,4)</f>
+        <f t="shared" si="124"/>
         <v>A038</v>
       </c>
       <c r="B875" t="str">
         <f>_xlfn.XLOOKUP(C875,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>9802</v>
+        <v>9502</v>
       </c>
       <c r="C875" t="s">
-        <v>1958</v>
+        <v>1949</v>
       </c>
       <c r="D875" t="s">
         <v>2802</v>
@@ -55942,11 +55999,11 @@
     </row>
     <row r="876" spans="1:5">
       <c r="A876" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="124"/>
         <v>A03A</v>
       </c>
       <c r="B876" t="str">
-        <f t="shared" ref="B876" si="160">RIGHT(DEC2HEX(C876,4),2)&amp;LEFT(DEC2HEX(C876,4),2)</f>
+        <f t="shared" ref="B876" si="159">RIGHT(DEC2HEX(C876,4),2)&amp;LEFT(DEC2HEX(C876,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C876">
@@ -55958,15 +56015,15 @@
     </row>
     <row r="877" spans="1:5">
       <c r="A877" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" ref="A877" si="160">DEC2HEX(HEX2DEC(A876)+LEN(B876)/2,4)</f>
         <v>A03C</v>
       </c>
       <c r="B877" t="str">
         <f>_xlfn.XLOOKUP(C877,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>AB01</v>
+        <v>9802</v>
       </c>
       <c r="C877" t="s">
-        <v>3884</v>
+        <v>1958</v>
       </c>
       <c r="D877" t="s">
         <v>2802</v>
@@ -55978,11 +56035,11 @@
     </row>
     <row r="878" spans="1:5">
       <c r="A878" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" ref="A877:A940" si="161">DEC2HEX(HEX2DEC(A877)+LEN(B877)/2,4)</f>
         <v>A03E</v>
       </c>
       <c r="B878" t="str">
-        <f t="shared" ref="B878" si="161">RIGHT(DEC2HEX(C878,4),2)&amp;LEFT(DEC2HEX(C878,4),2)</f>
+        <f t="shared" ref="B878" si="162">RIGHT(DEC2HEX(C878,4),2)&amp;LEFT(DEC2HEX(C878,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C878">
@@ -55994,15 +56051,15 @@
     </row>
     <row r="879" spans="1:5">
       <c r="A879" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A040</v>
       </c>
       <c r="B879" t="str">
         <f>_xlfn.XLOOKUP(C879,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>FF02</v>
+        <v>AB01</v>
       </c>
       <c r="C879" t="s">
-        <v>2260</v>
+        <v>3884</v>
       </c>
       <c r="D879" t="s">
         <v>2802</v>
@@ -56014,11 +56071,11 @@
     </row>
     <row r="880" spans="1:5">
       <c r="A880" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A042</v>
       </c>
       <c r="B880" t="str">
-        <f t="shared" ref="B880" si="162">RIGHT(DEC2HEX(C880,4),2)&amp;LEFT(DEC2HEX(C880,4),2)</f>
+        <f t="shared" ref="B880" si="163">RIGHT(DEC2HEX(C880,4),2)&amp;LEFT(DEC2HEX(C880,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C880">
@@ -56030,15 +56087,15 @@
     </row>
     <row r="881" spans="1:5">
       <c r="A881" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A044</v>
       </c>
       <c r="B881" t="str">
         <f>_xlfn.XLOOKUP(C881,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>6103</v>
+        <v>FF02</v>
       </c>
       <c r="C881" t="s">
-        <v>3897</v>
+        <v>2260</v>
       </c>
       <c r="D881" t="s">
         <v>2802</v>
@@ -56050,11 +56107,11 @@
     </row>
     <row r="882" spans="1:5">
       <c r="A882" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A046</v>
       </c>
       <c r="B882" t="str">
-        <f t="shared" ref="B882" si="163">RIGHT(DEC2HEX(C882,4),2)&amp;LEFT(DEC2HEX(C882,4),2)</f>
+        <f t="shared" ref="B882" si="164">RIGHT(DEC2HEX(C882,4),2)&amp;LEFT(DEC2HEX(C882,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C882">
@@ -56066,15 +56123,15 @@
     </row>
     <row r="883" spans="1:5">
       <c r="A883" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A048</v>
       </c>
       <c r="B883" t="str">
         <f>_xlfn.XLOOKUP(C883,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>9402</v>
+        <v>6103</v>
       </c>
       <c r="C883" t="s">
-        <v>1946</v>
+        <v>3897</v>
       </c>
       <c r="D883" t="s">
         <v>2802</v>
@@ -56086,11 +56143,11 @@
     </row>
     <row r="884" spans="1:5">
       <c r="A884" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A04A</v>
       </c>
       <c r="B884" t="str">
-        <f t="shared" ref="B884" si="164">RIGHT(DEC2HEX(C884,4),2)&amp;LEFT(DEC2HEX(C884,4),2)</f>
+        <f t="shared" ref="B884" si="165">RIGHT(DEC2HEX(C884,4),2)&amp;LEFT(DEC2HEX(C884,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C884">
@@ -56102,15 +56159,15 @@
     </row>
     <row r="885" spans="1:5">
       <c r="A885" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A04C</v>
       </c>
       <c r="B885" t="str">
         <f>_xlfn.XLOOKUP(C885,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>A602</v>
+        <v>9402</v>
       </c>
       <c r="C885" t="s">
-        <v>2000</v>
+        <v>1946</v>
       </c>
       <c r="D885" t="s">
         <v>2802</v>
@@ -56122,11 +56179,11 @@
     </row>
     <row r="886" spans="1:5">
       <c r="A886" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A04E</v>
       </c>
       <c r="B886" t="str">
-        <f t="shared" ref="B886" si="165">RIGHT(DEC2HEX(C886,4),2)&amp;LEFT(DEC2HEX(C886,4),2)</f>
+        <f t="shared" ref="B886" si="166">RIGHT(DEC2HEX(C886,4),2)&amp;LEFT(DEC2HEX(C886,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C886">
@@ -56138,15 +56195,15 @@
     </row>
     <row r="887" spans="1:5">
       <c r="A887" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A050</v>
       </c>
       <c r="B887" t="str">
         <f>_xlfn.XLOOKUP(C887,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>6C03</v>
+        <v>A602</v>
       </c>
       <c r="C887" t="s">
-        <v>3944</v>
+        <v>2000</v>
       </c>
       <c r="D887" t="s">
         <v>2802</v>
@@ -56158,11 +56215,11 @@
     </row>
     <row r="888" spans="1:5">
       <c r="A888" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A052</v>
       </c>
       <c r="B888" t="str">
-        <f t="shared" ref="B888" si="166">RIGHT(DEC2HEX(C888,4),2)&amp;LEFT(DEC2HEX(C888,4),2)</f>
+        <f t="shared" ref="B888" si="167">RIGHT(DEC2HEX(C888,4),2)&amp;LEFT(DEC2HEX(C888,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C888">
@@ -56174,15 +56231,15 @@
     </row>
     <row r="889" spans="1:5">
       <c r="A889" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A054</v>
       </c>
       <c r="B889" t="str">
         <f>_xlfn.XLOOKUP(C889,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>8400</v>
+        <v>6C03</v>
       </c>
       <c r="C889" t="s">
-        <v>3882</v>
+        <v>3944</v>
       </c>
       <c r="D889" t="s">
         <v>2802</v>
@@ -56194,11 +56251,11 @@
     </row>
     <row r="890" spans="1:5">
       <c r="A890" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A056</v>
       </c>
       <c r="B890" t="str">
-        <f t="shared" ref="B890" si="167">RIGHT(DEC2HEX(C890,4),2)&amp;LEFT(DEC2HEX(C890,4),2)</f>
+        <f t="shared" ref="B890" si="168">RIGHT(DEC2HEX(C890,4),2)&amp;LEFT(DEC2HEX(C890,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C890">
@@ -56210,15 +56267,15 @@
     </row>
     <row r="891" spans="1:5">
       <c r="A891" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A058</v>
       </c>
       <c r="B891" t="str">
         <f>_xlfn.XLOOKUP(C891,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>6203</v>
+        <v>8400</v>
       </c>
       <c r="C891" t="s">
-        <v>3898</v>
+        <v>3882</v>
       </c>
       <c r="D891" t="s">
         <v>2802</v>
@@ -56230,11 +56287,11 @@
     </row>
     <row r="892" spans="1:5">
       <c r="A892" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A05A</v>
       </c>
       <c r="B892" t="str">
-        <f t="shared" ref="B892" si="168">RIGHT(DEC2HEX(C892,4),2)&amp;LEFT(DEC2HEX(C892,4),2)</f>
+        <f t="shared" ref="B892" si="169">RIGHT(DEC2HEX(C892,4),2)&amp;LEFT(DEC2HEX(C892,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C892">
@@ -56246,15 +56303,15 @@
     </row>
     <row r="893" spans="1:5">
       <c r="A893" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A05C</v>
       </c>
       <c r="B893" t="str">
         <f>_xlfn.XLOOKUP(C893,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>6303</v>
+        <v>6203</v>
       </c>
       <c r="C893" t="s">
-        <v>3899</v>
+        <v>3898</v>
       </c>
       <c r="D893" t="s">
         <v>2802</v>
@@ -56266,11 +56323,11 @@
     </row>
     <row r="894" spans="1:5">
       <c r="A894" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A05E</v>
       </c>
       <c r="B894" t="str">
-        <f t="shared" ref="B894" si="169">RIGHT(DEC2HEX(C894,4),2)&amp;LEFT(DEC2HEX(C894,4),2)</f>
+        <f t="shared" ref="B894" si="170">RIGHT(DEC2HEX(C894,4),2)&amp;LEFT(DEC2HEX(C894,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C894">
@@ -56282,15 +56339,15 @@
     </row>
     <row r="895" spans="1:5">
       <c r="A895" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A060</v>
       </c>
       <c r="B895" t="str">
         <f>_xlfn.XLOOKUP(C895,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>8500</v>
+        <v>6303</v>
       </c>
       <c r="C895" t="s">
-        <v>3883</v>
+        <v>3899</v>
       </c>
       <c r="D895" t="s">
         <v>2802</v>
@@ -56302,11 +56359,11 @@
     </row>
     <row r="896" spans="1:5">
       <c r="A896" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A062</v>
       </c>
       <c r="B896" t="str">
-        <f t="shared" ref="B896" si="170">RIGHT(DEC2HEX(C896,4),2)&amp;LEFT(DEC2HEX(C896,4),2)</f>
+        <f t="shared" ref="B896" si="171">RIGHT(DEC2HEX(C896,4),2)&amp;LEFT(DEC2HEX(C896,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C896">
@@ -56318,15 +56375,15 @@
     </row>
     <row r="897" spans="1:5">
       <c r="A897" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A064</v>
       </c>
       <c r="B897" t="str">
         <f>_xlfn.XLOOKUP(C897,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>5B03</v>
+        <v>7503</v>
       </c>
       <c r="C897" t="s">
-        <v>3893</v>
+        <v>3946</v>
       </c>
       <c r="D897" t="s">
         <v>2802</v>
@@ -56338,11 +56395,11 @@
     </row>
     <row r="898" spans="1:5">
       <c r="A898" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A066</v>
       </c>
       <c r="B898" t="str">
-        <f t="shared" ref="B898" si="171">RIGHT(DEC2HEX(C898,4),2)&amp;LEFT(DEC2HEX(C898,4),2)</f>
+        <f t="shared" ref="B898" si="172">RIGHT(DEC2HEX(C898,4),2)&amp;LEFT(DEC2HEX(C898,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C898">
@@ -56354,15 +56411,15 @@
     </row>
     <row r="899" spans="1:5">
       <c r="A899" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A068</v>
       </c>
       <c r="B899" t="str">
         <f>_xlfn.XLOOKUP(C899,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>6403</v>
+        <v>8500</v>
       </c>
       <c r="C899" t="s">
-        <v>3900</v>
+        <v>3883</v>
       </c>
       <c r="D899" t="s">
         <v>2802</v>
@@ -56374,12 +56431,15 @@
     </row>
     <row r="900" spans="1:5">
       <c r="A900" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A06A</v>
       </c>
       <c r="B900" t="str">
-        <f t="shared" ref="B900" si="172">RIGHT(DEC2HEX(C900,4),2)&amp;LEFT(DEC2HEX(C900,4),2)</f>
-        <v>0000</v>
+        <f t="shared" ref="B900" si="173">RIGHT(DEC2HEX(C900,4),2)&amp;LEFT(DEC2HEX(C900,4),2)</f>
+        <v>1400</v>
+      </c>
+      <c r="C900">
+        <v>20</v>
       </c>
       <c r="D900" t="s">
         <v>2802</v>
@@ -56387,15 +56447,15 @@
     </row>
     <row r="901" spans="1:5">
       <c r="A901" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A06C</v>
       </c>
       <c r="B901" t="str">
         <f>_xlfn.XLOOKUP(C901,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>8200</v>
+        <v>7E03</v>
       </c>
       <c r="C901" t="s">
-        <v>3880</v>
+        <v>3956</v>
       </c>
       <c r="D901" t="s">
         <v>2802</v>
@@ -56407,11 +56467,11 @@
     </row>
     <row r="902" spans="1:5">
       <c r="A902" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A06E</v>
       </c>
       <c r="B902" t="str">
-        <f t="shared" ref="B902" si="173">RIGHT(DEC2HEX(C902,4),2)&amp;LEFT(DEC2HEX(C902,4),2)</f>
+        <f t="shared" ref="B902" si="174">RIGHT(DEC2HEX(C902,4),2)&amp;LEFT(DEC2HEX(C902,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C902">
@@ -56423,15 +56483,15 @@
     </row>
     <row r="903" spans="1:5">
       <c r="A903" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A070</v>
       </c>
       <c r="B903" t="str">
         <f>_xlfn.XLOOKUP(C903,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>6603</v>
+        <v>5B03</v>
       </c>
       <c r="C903" t="s">
-        <v>3902</v>
+        <v>3893</v>
       </c>
       <c r="D903" t="s">
         <v>2802</v>
@@ -56443,11 +56503,11 @@
     </row>
     <row r="904" spans="1:5">
       <c r="A904" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A072</v>
       </c>
       <c r="B904" t="str">
-        <f t="shared" ref="B904" si="174">RIGHT(DEC2HEX(C904,4),2)&amp;LEFT(DEC2HEX(C904,4),2)</f>
+        <f t="shared" ref="B904" si="175">RIGHT(DEC2HEX(C904,4),2)&amp;LEFT(DEC2HEX(C904,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C904">
@@ -56459,15 +56519,15 @@
     </row>
     <row r="905" spans="1:5">
       <c r="A905" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A074</v>
       </c>
       <c r="B905" t="str">
         <f>_xlfn.XLOOKUP(C905,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>F402</v>
+        <v>7603</v>
       </c>
       <c r="C905" t="s">
-        <v>2227</v>
+        <v>3947</v>
       </c>
       <c r="D905" t="s">
         <v>2802</v>
@@ -56479,11 +56539,11 @@
     </row>
     <row r="906" spans="1:5">
       <c r="A906" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A076</v>
       </c>
       <c r="B906" t="str">
-        <f t="shared" ref="B906" si="175">RIGHT(DEC2HEX(C906,4),2)&amp;LEFT(DEC2HEX(C906,4),2)</f>
+        <f t="shared" ref="B906:B912" si="176">RIGHT(DEC2HEX(C906,4),2)&amp;LEFT(DEC2HEX(C906,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C906">
@@ -56495,15 +56555,15 @@
     </row>
     <row r="907" spans="1:5">
       <c r="A907" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A078</v>
       </c>
       <c r="B907" t="str">
         <f>_xlfn.XLOOKUP(C907,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>6703</v>
+        <v>7F03</v>
       </c>
       <c r="C907" t="s">
-        <v>3903</v>
+        <v>3957</v>
       </c>
       <c r="D907" t="s">
         <v>2802</v>
@@ -56515,15 +56575,15 @@
     </row>
     <row r="908" spans="1:5">
       <c r="A908" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A07A</v>
       </c>
       <c r="B908" t="str">
-        <f t="shared" ref="B908" si="176">RIGHT(DEC2HEX(C908,4),2)&amp;LEFT(DEC2HEX(C908,4),2)</f>
-        <v>0A00</v>
+        <f t="shared" ref="B908" si="177">RIGHT(DEC2HEX(C908,4),2)&amp;LEFT(DEC2HEX(C908,4),2)</f>
+        <v>1400</v>
       </c>
       <c r="C908">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D908" t="s">
         <v>2802</v>
@@ -56531,15 +56591,15 @@
     </row>
     <row r="909" spans="1:5">
       <c r="A909" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A07C</v>
       </c>
       <c r="B909" t="str">
         <f>_xlfn.XLOOKUP(C909,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>AB02</v>
+        <v>7703</v>
       </c>
       <c r="C909" t="s">
-        <v>2015</v>
+        <v>3949</v>
       </c>
       <c r="D909" t="s">
         <v>2802</v>
@@ -56551,11 +56611,11 @@
     </row>
     <row r="910" spans="1:5">
       <c r="A910" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A07E</v>
       </c>
       <c r="B910" t="str">
-        <f t="shared" ref="B910" si="177">RIGHT(DEC2HEX(C910,4),2)&amp;LEFT(DEC2HEX(C910,4),2)</f>
+        <f t="shared" si="176"/>
         <v>1400</v>
       </c>
       <c r="C910">
@@ -56567,15 +56627,15 @@
     </row>
     <row r="911" spans="1:5">
       <c r="A911" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A080</v>
       </c>
       <c r="B911" t="str">
         <f>_xlfn.XLOOKUP(C911,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>9102</v>
+        <v>7803</v>
       </c>
       <c r="C911" t="s">
-        <v>1937</v>
+        <v>3948</v>
       </c>
       <c r="D911" t="s">
         <v>2802</v>
@@ -56587,11 +56647,11 @@
     </row>
     <row r="912" spans="1:5">
       <c r="A912" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A082</v>
       </c>
       <c r="B912" t="str">
-        <f t="shared" ref="B912" si="178">RIGHT(DEC2HEX(C912,4),2)&amp;LEFT(DEC2HEX(C912,4),2)</f>
+        <f t="shared" si="176"/>
         <v>1400</v>
       </c>
       <c r="C912">
@@ -56603,15 +56663,15 @@
     </row>
     <row r="913" spans="1:5">
       <c r="A913" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A084</v>
       </c>
       <c r="B913" t="str">
         <f>_xlfn.XLOOKUP(C913,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>9002</v>
+        <v>6403</v>
       </c>
       <c r="C913" t="s">
-        <v>1934</v>
+        <v>3900</v>
       </c>
       <c r="D913" t="s">
         <v>2802</v>
@@ -56623,11 +56683,11 @@
     </row>
     <row r="914" spans="1:5">
       <c r="A914" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A086</v>
       </c>
       <c r="B914" t="str">
-        <f t="shared" ref="B914" si="179">RIGHT(DEC2HEX(C914,4),2)&amp;LEFT(DEC2HEX(C914,4),2)</f>
+        <f t="shared" ref="B914" si="178">RIGHT(DEC2HEX(C914,4),2)&amp;LEFT(DEC2HEX(C914,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C914">
@@ -56639,15 +56699,15 @@
     </row>
     <row r="915" spans="1:5">
       <c r="A915" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A088</v>
       </c>
       <c r="B915" t="str">
         <f>_xlfn.XLOOKUP(C915,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>FB02</v>
+        <v>8200</v>
       </c>
       <c r="C915" t="s">
-        <v>2248</v>
+        <v>3880</v>
       </c>
       <c r="D915" t="s">
         <v>2802</v>
@@ -56659,11 +56719,11 @@
     </row>
     <row r="916" spans="1:5">
       <c r="A916" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A08A</v>
       </c>
       <c r="B916" t="str">
-        <f t="shared" ref="B916" si="180">RIGHT(DEC2HEX(C916,4),2)&amp;LEFT(DEC2HEX(C916,4),2)</f>
+        <f t="shared" ref="B916" si="179">RIGHT(DEC2HEX(C916,4),2)&amp;LEFT(DEC2HEX(C916,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C916">
@@ -56675,15 +56735,15 @@
     </row>
     <row r="917" spans="1:5">
       <c r="A917" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A08C</v>
       </c>
       <c r="B917" t="str">
         <f>_xlfn.XLOOKUP(C917,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>4803</v>
+        <v>6603</v>
       </c>
       <c r="C917" t="s">
-        <v>3888</v>
+        <v>3902</v>
       </c>
       <c r="D917" t="s">
         <v>2802</v>
@@ -56695,11 +56755,11 @@
     </row>
     <row r="918" spans="1:5">
       <c r="A918" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A08E</v>
       </c>
       <c r="B918" t="str">
-        <f t="shared" ref="B918" si="181">RIGHT(DEC2HEX(C918,4),2)&amp;LEFT(DEC2HEX(C918,4),2)</f>
+        <f t="shared" ref="B918" si="180">RIGHT(DEC2HEX(C918,4),2)&amp;LEFT(DEC2HEX(C918,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C918">
@@ -56711,15 +56771,15 @@
     </row>
     <row r="919" spans="1:5">
       <c r="A919" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A090</v>
       </c>
       <c r="B919" t="str">
         <f>_xlfn.XLOOKUP(C919,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>A402</v>
+        <v>F402</v>
       </c>
       <c r="C919" t="s">
-        <v>1994</v>
+        <v>2227</v>
       </c>
       <c r="D919" t="s">
         <v>2802</v>
@@ -56731,11 +56791,11 @@
     </row>
     <row r="920" spans="1:5">
       <c r="A920" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A092</v>
       </c>
       <c r="B920" t="str">
-        <f t="shared" ref="B920" si="182">RIGHT(DEC2HEX(C920,4),2)&amp;LEFT(DEC2HEX(C920,4),2)</f>
+        <f t="shared" ref="B920" si="181">RIGHT(DEC2HEX(C920,4),2)&amp;LEFT(DEC2HEX(C920,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C920">
@@ -56747,15 +56807,15 @@
     </row>
     <row r="921" spans="1:5">
       <c r="A921" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A094</v>
       </c>
       <c r="B921" t="str">
         <f>_xlfn.XLOOKUP(C921,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>A802</v>
+        <v>6703</v>
       </c>
       <c r="C921" t="s">
-        <v>2006</v>
+        <v>3903</v>
       </c>
       <c r="D921" t="s">
         <v>2802</v>
@@ -56767,11 +56827,11 @@
     </row>
     <row r="922" spans="1:5">
       <c r="A922" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A096</v>
       </c>
       <c r="B922" t="str">
-        <f t="shared" ref="B922" si="183">RIGHT(DEC2HEX(C922,4),2)&amp;LEFT(DEC2HEX(C922,4),2)</f>
+        <f t="shared" ref="B922" si="182">RIGHT(DEC2HEX(C922,4),2)&amp;LEFT(DEC2HEX(C922,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C922">
@@ -56783,15 +56843,15 @@
     </row>
     <row r="923" spans="1:5">
       <c r="A923" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A098</v>
       </c>
       <c r="B923" t="str">
         <f>_xlfn.XLOOKUP(C923,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>9A02</v>
+        <v>AB02</v>
       </c>
       <c r="C923" t="s">
-        <v>1964</v>
+        <v>2015</v>
       </c>
       <c r="D923" t="s">
         <v>2802</v>
@@ -56803,11 +56863,11 @@
     </row>
     <row r="924" spans="1:5">
       <c r="A924" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A09A</v>
       </c>
       <c r="B924" t="str">
-        <f t="shared" ref="B924" si="184">RIGHT(DEC2HEX(C924,4),2)&amp;LEFT(DEC2HEX(C924,4),2)</f>
+        <f t="shared" ref="B924" si="183">RIGHT(DEC2HEX(C924,4),2)&amp;LEFT(DEC2HEX(C924,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C924">
@@ -56819,15 +56879,15 @@
     </row>
     <row r="925" spans="1:5">
       <c r="A925" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A09C</v>
       </c>
       <c r="B925" t="str">
         <f>_xlfn.XLOOKUP(C925,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>A302</v>
+        <v>9102</v>
       </c>
       <c r="C925" t="s">
-        <v>1991</v>
+        <v>1937</v>
       </c>
       <c r="D925" t="s">
         <v>2802</v>
@@ -56839,11 +56899,11 @@
     </row>
     <row r="926" spans="1:5">
       <c r="A926" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A09E</v>
       </c>
       <c r="B926" t="str">
-        <f t="shared" ref="B926" si="185">RIGHT(DEC2HEX(C926,4),2)&amp;LEFT(DEC2HEX(C926,4),2)</f>
+        <f t="shared" ref="B926" si="184">RIGHT(DEC2HEX(C926,4),2)&amp;LEFT(DEC2HEX(C926,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C926">
@@ -56855,15 +56915,15 @@
     </row>
     <row r="927" spans="1:5">
       <c r="A927" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A0A0</v>
       </c>
       <c r="B927" t="str">
         <f>_xlfn.XLOOKUP(C927,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>7F00</v>
+        <v>9002</v>
       </c>
       <c r="C927" t="s">
-        <v>3877</v>
+        <v>1934</v>
       </c>
       <c r="D927" t="s">
         <v>2802</v>
@@ -56875,11 +56935,11 @@
     </row>
     <row r="928" spans="1:5">
       <c r="A928" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A0A2</v>
       </c>
       <c r="B928" t="str">
-        <f t="shared" ref="B928" si="186">RIGHT(DEC2HEX(C928,4),2)&amp;LEFT(DEC2HEX(C928,4),2)</f>
+        <f t="shared" ref="B928" si="185">RIGHT(DEC2HEX(C928,4),2)&amp;LEFT(DEC2HEX(C928,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C928">
@@ -56891,15 +56951,15 @@
     </row>
     <row r="929" spans="1:5">
       <c r="A929" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A0A4</v>
       </c>
       <c r="B929" t="str">
         <f>_xlfn.XLOOKUP(C929,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>8300</v>
+        <v>FB02</v>
       </c>
       <c r="C929" t="s">
-        <v>3881</v>
+        <v>2248</v>
       </c>
       <c r="D929" t="s">
         <v>2802</v>
@@ -56911,11 +56971,11 @@
     </row>
     <row r="930" spans="1:5">
       <c r="A930" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A0A6</v>
       </c>
       <c r="B930" t="str">
-        <f t="shared" ref="B930" si="187">RIGHT(DEC2HEX(C930,4),2)&amp;LEFT(DEC2HEX(C930,4),2)</f>
+        <f t="shared" ref="B930" si="186">RIGHT(DEC2HEX(C930,4),2)&amp;LEFT(DEC2HEX(C930,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C930">
@@ -56927,15 +56987,15 @@
     </row>
     <row r="931" spans="1:5">
       <c r="A931" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A0A8</v>
       </c>
       <c r="B931" t="str">
         <f>_xlfn.XLOOKUP(C931,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>AC02</v>
+        <v>4803</v>
       </c>
       <c r="C931" t="s">
-        <v>2018</v>
+        <v>3888</v>
       </c>
       <c r="D931" t="s">
         <v>2802</v>
@@ -56947,11 +57007,11 @@
     </row>
     <row r="932" spans="1:5">
       <c r="A932" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A0AA</v>
       </c>
       <c r="B932" t="str">
-        <f t="shared" ref="B932" si="188">RIGHT(DEC2HEX(C932,4),2)&amp;LEFT(DEC2HEX(C932,4),2)</f>
+        <f t="shared" ref="B932" si="187">RIGHT(DEC2HEX(C932,4),2)&amp;LEFT(DEC2HEX(C932,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C932">
@@ -56963,15 +57023,15 @@
     </row>
     <row r="933" spans="1:5">
       <c r="A933" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A0AC</v>
       </c>
       <c r="B933" t="str">
         <f>_xlfn.XLOOKUP(C933,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>AD02</v>
+        <v>8003</v>
       </c>
       <c r="C933" t="s">
-        <v>2021</v>
+        <v>3958</v>
       </c>
       <c r="D933" t="s">
         <v>2802</v>
@@ -56983,11 +57043,11 @@
     </row>
     <row r="934" spans="1:5">
       <c r="A934" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A0AE</v>
       </c>
       <c r="B934" t="str">
-        <f t="shared" ref="B934" si="189">RIGHT(DEC2HEX(C934,4),2)&amp;LEFT(DEC2HEX(C934,4),2)</f>
+        <f t="shared" ref="B934" si="188">RIGHT(DEC2HEX(C934,4),2)&amp;LEFT(DEC2HEX(C934,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C934">
@@ -56999,15 +57059,15 @@
     </row>
     <row r="935" spans="1:5">
       <c r="A935" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A0B0</v>
       </c>
       <c r="B935" t="str">
         <f>_xlfn.XLOOKUP(C935,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>0003</v>
+        <v>A402</v>
       </c>
       <c r="C935" t="s">
-        <v>2262</v>
+        <v>1994</v>
       </c>
       <c r="D935" t="s">
         <v>2802</v>
@@ -57019,11 +57079,11 @@
     </row>
     <row r="936" spans="1:5">
       <c r="A936" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A0B2</v>
       </c>
       <c r="B936" t="str">
-        <f t="shared" ref="B936" si="190">RIGHT(DEC2HEX(C936,4),2)&amp;LEFT(DEC2HEX(C936,4),2)</f>
+        <f t="shared" ref="B936:B938" si="189">RIGHT(DEC2HEX(C936,4),2)&amp;LEFT(DEC2HEX(C936,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C936">
@@ -57035,15 +57095,15 @@
     </row>
     <row r="937" spans="1:5">
       <c r="A937" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A0B4</v>
       </c>
       <c r="B937" t="str">
         <f>_xlfn.XLOOKUP(C937,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>A102</v>
+        <v>7903</v>
       </c>
       <c r="C937" t="s">
-        <v>1985</v>
+        <v>3950</v>
       </c>
       <c r="D937" t="s">
         <v>2802</v>
@@ -57055,11 +57115,11 @@
     </row>
     <row r="938" spans="1:5">
       <c r="A938" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>A0B6</v>
       </c>
       <c r="B938" t="str">
-        <f t="shared" ref="B938" si="191">RIGHT(DEC2HEX(C938,4),2)&amp;LEFT(DEC2HEX(C938,4),2)</f>
+        <f t="shared" si="189"/>
         <v>1400</v>
       </c>
       <c r="C938">
@@ -57071,15 +57131,15 @@
     </row>
     <row r="939" spans="1:5">
       <c r="A939" t="str">
-        <f t="shared" ref="A939:A940" si="192">DEC2HEX(HEX2DEC(A938)+LEN(B938)/2,4)</f>
+        <f t="shared" si="161"/>
         <v>A0B8</v>
       </c>
       <c r="B939" t="str">
         <f>_xlfn.XLOOKUP(C939,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>6A03</v>
+        <v>A802</v>
       </c>
       <c r="C939" t="s">
-        <v>3942</v>
+        <v>2006</v>
       </c>
       <c r="D939" t="s">
         <v>2802</v>
@@ -57091,11 +57151,11 @@
     </row>
     <row r="940" spans="1:5">
       <c r="A940" t="str">
-        <f t="shared" si="192"/>
+        <f t="shared" si="161"/>
         <v>A0BA</v>
       </c>
       <c r="B940" t="str">
-        <f t="shared" ref="B940" si="193">RIGHT(DEC2HEX(C940,4),2)&amp;LEFT(DEC2HEX(C940,4),2)</f>
+        <f t="shared" ref="B940" si="190">RIGHT(DEC2HEX(C940,4),2)&amp;LEFT(DEC2HEX(C940,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C940">
@@ -57107,15 +57167,15 @@
     </row>
     <row r="941" spans="1:5">
       <c r="A941" t="str">
-        <f t="shared" ref="A939:A971" si="194">DEC2HEX(HEX2DEC(A940)+LEN(B940)/2,4)</f>
+        <f t="shared" ref="A941:A1004" si="191">DEC2HEX(HEX2DEC(A940)+LEN(B940)/2,4)</f>
         <v>A0BC</v>
       </c>
       <c r="B941" t="str">
         <f>_xlfn.XLOOKUP(C941,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>6903</v>
+        <v>9A02</v>
       </c>
       <c r="C941" t="s">
-        <v>3941</v>
+        <v>1964</v>
       </c>
       <c r="D941" t="s">
         <v>2802</v>
@@ -57127,11 +57187,11 @@
     </row>
     <row r="942" spans="1:5">
       <c r="A942" t="str">
-        <f t="shared" si="194"/>
+        <f t="shared" si="191"/>
         <v>A0BE</v>
       </c>
       <c r="B942" t="str">
-        <f t="shared" ref="B942" si="195">RIGHT(DEC2HEX(C942,4),2)&amp;LEFT(DEC2HEX(C942,4),2)</f>
+        <f t="shared" ref="B942" si="192">RIGHT(DEC2HEX(C942,4),2)&amp;LEFT(DEC2HEX(C942,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C942">
@@ -57143,15 +57203,15 @@
     </row>
     <row r="943" spans="1:5">
       <c r="A943" t="str">
-        <f t="shared" si="194"/>
+        <f t="shared" si="191"/>
         <v>A0C0</v>
       </c>
       <c r="B943" t="str">
         <f>_xlfn.XLOOKUP(C943,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>6003</v>
+        <v>A302</v>
       </c>
       <c r="C943" t="s">
-        <v>3896</v>
+        <v>1991</v>
       </c>
       <c r="D943" t="s">
         <v>2802</v>
@@ -57163,11 +57223,11 @@
     </row>
     <row r="944" spans="1:5">
       <c r="A944" t="str">
-        <f t="shared" si="194"/>
+        <f t="shared" si="191"/>
         <v>A0C2</v>
       </c>
       <c r="B944" t="str">
-        <f t="shared" ref="B944" si="196">RIGHT(DEC2HEX(C944,4),2)&amp;LEFT(DEC2HEX(C944,4),2)</f>
+        <f t="shared" ref="B944" si="193">RIGHT(DEC2HEX(C944,4),2)&amp;LEFT(DEC2HEX(C944,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C944">
@@ -57179,15 +57239,15 @@
     </row>
     <row r="945" spans="1:5">
       <c r="A945" t="str">
-        <f t="shared" si="194"/>
+        <f t="shared" si="191"/>
         <v>A0C4</v>
       </c>
       <c r="B945" t="str">
         <f>_xlfn.XLOOKUP(C945,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>AA02</v>
+        <v>7F00</v>
       </c>
       <c r="C945" t="s">
-        <v>2012</v>
+        <v>3877</v>
       </c>
       <c r="D945" t="s">
         <v>2802</v>
@@ -57199,11 +57259,11 @@
     </row>
     <row r="946" spans="1:5">
       <c r="A946" t="str">
-        <f t="shared" si="194"/>
+        <f t="shared" si="191"/>
         <v>A0C6</v>
       </c>
       <c r="B946" t="str">
-        <f t="shared" ref="B946" si="197">RIGHT(DEC2HEX(C946,4),2)&amp;LEFT(DEC2HEX(C946,4),2)</f>
+        <f t="shared" ref="B946" si="194">RIGHT(DEC2HEX(C946,4),2)&amp;LEFT(DEC2HEX(C946,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C946">
@@ -57215,15 +57275,15 @@
     </row>
     <row r="947" spans="1:5">
       <c r="A947" t="str">
-        <f t="shared" si="194"/>
+        <f t="shared" si="191"/>
         <v>A0C8</v>
       </c>
       <c r="B947" t="str">
         <f>_xlfn.XLOOKUP(C947,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>A902</v>
+        <v>8300</v>
       </c>
       <c r="C947" t="s">
-        <v>2009</v>
+        <v>3881</v>
       </c>
       <c r="D947" t="s">
         <v>2802</v>
@@ -57235,11 +57295,11 @@
     </row>
     <row r="948" spans="1:5">
       <c r="A948" t="str">
-        <f t="shared" si="194"/>
+        <f t="shared" si="191"/>
         <v>A0CA</v>
       </c>
       <c r="B948" t="str">
-        <f t="shared" ref="B948" si="198">RIGHT(DEC2HEX(C948,4),2)&amp;LEFT(DEC2HEX(C948,4),2)</f>
+        <f t="shared" ref="B948" si="195">RIGHT(DEC2HEX(C948,4),2)&amp;LEFT(DEC2HEX(C948,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C948">
@@ -57251,15 +57311,15 @@
     </row>
     <row r="949" spans="1:5">
       <c r="A949" t="str">
-        <f t="shared" si="194"/>
+        <f t="shared" si="191"/>
         <v>A0CC</v>
       </c>
       <c r="B949" t="str">
         <f>_xlfn.XLOOKUP(C949,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>9902</v>
+        <v>AC02</v>
       </c>
       <c r="C949" t="s">
-        <v>1961</v>
+        <v>2018</v>
       </c>
       <c r="D949" t="s">
         <v>2802</v>
@@ -57271,11 +57331,11 @@
     </row>
     <row r="950" spans="1:5">
       <c r="A950" t="str">
-        <f t="shared" si="194"/>
+        <f t="shared" si="191"/>
         <v>A0CE</v>
       </c>
       <c r="B950" t="str">
-        <f t="shared" ref="B950:B952" si="199">RIGHT(DEC2HEX(C950,4),2)&amp;LEFT(DEC2HEX(C950,4),2)</f>
+        <f t="shared" ref="B950" si="196">RIGHT(DEC2HEX(C950,4),2)&amp;LEFT(DEC2HEX(C950,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C950">
@@ -57287,15 +57347,15 @@
     </row>
     <row r="951" spans="1:5">
       <c r="A951" t="str">
-        <f t="shared" si="194"/>
+        <f t="shared" si="191"/>
         <v>A0D0</v>
       </c>
       <c r="B951" t="str">
         <f>_xlfn.XLOOKUP(C951,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>6803</v>
+        <v>AD02</v>
       </c>
       <c r="C951" t="s">
-        <v>3940</v>
+        <v>2021</v>
       </c>
       <c r="D951" t="s">
         <v>2802</v>
@@ -57307,11 +57367,11 @@
     </row>
     <row r="952" spans="1:5">
       <c r="A952" t="str">
-        <f t="shared" si="194"/>
+        <f t="shared" si="191"/>
         <v>A0D2</v>
       </c>
       <c r="B952" t="str">
-        <f t="shared" si="199"/>
+        <f t="shared" ref="B952" si="197">RIGHT(DEC2HEX(C952,4),2)&amp;LEFT(DEC2HEX(C952,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C952">
@@ -57323,15 +57383,15 @@
     </row>
     <row r="953" spans="1:5">
       <c r="A953" t="str">
-        <f t="shared" si="194"/>
+        <f t="shared" si="191"/>
         <v>A0D4</v>
       </c>
       <c r="B953" t="str">
         <f>_xlfn.XLOOKUP(C953,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>F602</v>
+        <v>0003</v>
       </c>
       <c r="C953" t="s">
-        <v>2233</v>
+        <v>2262</v>
       </c>
       <c r="D953" t="s">
         <v>2802</v>
@@ -57343,11 +57403,11 @@
     </row>
     <row r="954" spans="1:5">
       <c r="A954" t="str">
-        <f t="shared" si="194"/>
+        <f t="shared" si="191"/>
         <v>A0D6</v>
       </c>
       <c r="B954" t="str">
-        <f t="shared" ref="B954" si="200">RIGHT(DEC2HEX(C954,4),2)&amp;LEFT(DEC2HEX(C954,4),2)</f>
+        <f t="shared" ref="B954" si="198">RIGHT(DEC2HEX(C954,4),2)&amp;LEFT(DEC2HEX(C954,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C954">
@@ -57359,15 +57419,15 @@
     </row>
     <row r="955" spans="1:5">
       <c r="A955" t="str">
-        <f t="shared" si="194"/>
+        <f t="shared" si="191"/>
         <v>A0D8</v>
       </c>
       <c r="B955" t="str">
         <f>_xlfn.XLOOKUP(C955,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>9602</v>
+        <v>A102</v>
       </c>
       <c r="C955" t="s">
-        <v>1952</v>
+        <v>1985</v>
       </c>
       <c r="D955" t="s">
         <v>2802</v>
@@ -57379,11 +57439,11 @@
     </row>
     <row r="956" spans="1:5">
       <c r="A956" t="str">
-        <f t="shared" si="194"/>
+        <f t="shared" si="191"/>
         <v>A0DA</v>
       </c>
       <c r="B956" t="str">
-        <f t="shared" ref="B956" si="201">RIGHT(DEC2HEX(C956,4),2)&amp;LEFT(DEC2HEX(C956,4),2)</f>
+        <f t="shared" ref="B956" si="199">RIGHT(DEC2HEX(C956,4),2)&amp;LEFT(DEC2HEX(C956,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C956">
@@ -57395,15 +57455,15 @@
     </row>
     <row r="957" spans="1:5">
       <c r="A957" t="str">
-        <f t="shared" si="194"/>
+        <f t="shared" si="191"/>
         <v>A0DC</v>
       </c>
       <c r="B957" t="str">
         <f>_xlfn.XLOOKUP(C957,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>9702</v>
+        <v>6A03</v>
       </c>
       <c r="C957" t="s">
-        <v>1955</v>
+        <v>3942</v>
       </c>
       <c r="D957" t="s">
         <v>2802</v>
@@ -57415,11 +57475,11 @@
     </row>
     <row r="958" spans="1:5">
       <c r="A958" t="str">
-        <f t="shared" si="194"/>
+        <f t="shared" si="191"/>
         <v>A0DE</v>
       </c>
       <c r="B958" t="str">
-        <f t="shared" ref="B958" si="202">RIGHT(DEC2HEX(C958,4),2)&amp;LEFT(DEC2HEX(C958,4),2)</f>
+        <f t="shared" ref="B958" si="200">RIGHT(DEC2HEX(C958,4),2)&amp;LEFT(DEC2HEX(C958,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C958">
@@ -57431,15 +57491,15 @@
     </row>
     <row r="959" spans="1:5">
       <c r="A959" t="str">
-        <f t="shared" si="194"/>
+        <f t="shared" si="191"/>
         <v>A0E0</v>
       </c>
       <c r="B959" t="str">
         <f>_xlfn.XLOOKUP(C959,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>FA02</v>
+        <v>6903</v>
       </c>
       <c r="C959" t="s">
-        <v>2245</v>
+        <v>3941</v>
       </c>
       <c r="D959" t="s">
         <v>2802</v>
@@ -57451,11 +57511,11 @@
     </row>
     <row r="960" spans="1:5">
       <c r="A960" t="str">
-        <f t="shared" si="194"/>
+        <f t="shared" si="191"/>
         <v>A0E2</v>
       </c>
       <c r="B960" t="str">
-        <f t="shared" ref="B960" si="203">RIGHT(DEC2HEX(C960,4),2)&amp;LEFT(DEC2HEX(C960,4),2)</f>
+        <f t="shared" ref="B960" si="201">RIGHT(DEC2HEX(C960,4),2)&amp;LEFT(DEC2HEX(C960,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C960">
@@ -57467,15 +57527,15 @@
     </row>
     <row r="961" spans="1:5">
       <c r="A961" t="str">
-        <f t="shared" si="194"/>
+        <f t="shared" si="191"/>
         <v>A0E4</v>
       </c>
       <c r="B961" t="str">
         <f>_xlfn.XLOOKUP(C961,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>9F02</v>
+        <v>6003</v>
       </c>
       <c r="C961" t="s">
-        <v>1979</v>
+        <v>3896</v>
       </c>
       <c r="D961" t="s">
         <v>2802</v>
@@ -57487,11 +57547,11 @@
     </row>
     <row r="962" spans="1:5">
       <c r="A962" t="str">
-        <f t="shared" si="194"/>
+        <f t="shared" si="191"/>
         <v>A0E6</v>
       </c>
       <c r="B962" t="str">
-        <f t="shared" ref="B962" si="204">RIGHT(DEC2HEX(C962,4),2)&amp;LEFT(DEC2HEX(C962,4),2)</f>
+        <f t="shared" ref="B962" si="202">RIGHT(DEC2HEX(C962,4),2)&amp;LEFT(DEC2HEX(C962,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C962">
@@ -57503,15 +57563,15 @@
     </row>
     <row r="963" spans="1:5">
       <c r="A963" t="str">
-        <f t="shared" si="194"/>
+        <f t="shared" si="191"/>
         <v>A0E8</v>
       </c>
       <c r="B963" t="str">
         <f>_xlfn.XLOOKUP(C963,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>6D03</v>
+        <v>8103</v>
       </c>
       <c r="C963" t="s">
-        <v>3945</v>
+        <v>3959</v>
       </c>
       <c r="D963" t="s">
         <v>2802</v>
@@ -57523,11 +57583,11 @@
     </row>
     <row r="964" spans="1:5">
       <c r="A964" t="str">
-        <f t="shared" si="194"/>
+        <f t="shared" si="191"/>
         <v>A0EA</v>
       </c>
       <c r="B964" t="str">
-        <f t="shared" ref="B964" si="205">RIGHT(DEC2HEX(C964,4),2)&amp;LEFT(DEC2HEX(C964,4),2)</f>
+        <f t="shared" ref="B964" si="203">RIGHT(DEC2HEX(C964,4),2)&amp;LEFT(DEC2HEX(C964,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C964">
@@ -57539,15 +57599,15 @@
     </row>
     <row r="965" spans="1:5">
       <c r="A965" t="str">
-        <f t="shared" si="194"/>
+        <f t="shared" si="191"/>
         <v>A0EC</v>
       </c>
       <c r="B965" t="str">
         <f>_xlfn.XLOOKUP(C965,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>F202</v>
+        <v>AA02</v>
       </c>
       <c r="C965" t="s">
-        <v>2221</v>
+        <v>2012</v>
       </c>
       <c r="D965" t="s">
         <v>2802</v>
@@ -57559,11 +57619,11 @@
     </row>
     <row r="966" spans="1:5">
       <c r="A966" t="str">
-        <f t="shared" si="194"/>
+        <f t="shared" si="191"/>
         <v>A0EE</v>
       </c>
       <c r="B966" t="str">
-        <f t="shared" ref="B966" si="206">RIGHT(DEC2HEX(C966,4),2)&amp;LEFT(DEC2HEX(C966,4),2)</f>
+        <f t="shared" ref="B966" si="204">RIGHT(DEC2HEX(C966,4),2)&amp;LEFT(DEC2HEX(C966,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C966">
@@ -57575,15 +57635,15 @@
     </row>
     <row r="967" spans="1:5">
       <c r="A967" t="str">
-        <f t="shared" si="194"/>
+        <f t="shared" si="191"/>
         <v>A0F0</v>
       </c>
       <c r="B967" t="str">
         <f>_xlfn.XLOOKUP(C967,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>0103</v>
+        <v>A902</v>
       </c>
       <c r="C967" t="s">
-        <v>2263</v>
+        <v>2009</v>
       </c>
       <c r="D967" t="s">
         <v>2802</v>
@@ -57595,11 +57655,11 @@
     </row>
     <row r="968" spans="1:5">
       <c r="A968" t="str">
-        <f t="shared" si="194"/>
+        <f t="shared" si="191"/>
         <v>A0F2</v>
       </c>
       <c r="B968" t="str">
-        <f t="shared" ref="B968" si="207">RIGHT(DEC2HEX(C968,4),2)&amp;LEFT(DEC2HEX(C968,4),2)</f>
+        <f t="shared" ref="B968" si="205">RIGHT(DEC2HEX(C968,4),2)&amp;LEFT(DEC2HEX(C968,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C968">
@@ -57611,15 +57671,15 @@
     </row>
     <row r="969" spans="1:5">
       <c r="A969" t="str">
-        <f t="shared" si="194"/>
+        <f t="shared" si="191"/>
         <v>A0F4</v>
       </c>
       <c r="B969" t="str">
         <f>_xlfn.XLOOKUP(C969,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>5E03</v>
+        <v>9902</v>
       </c>
       <c r="C969" t="s">
-        <v>3894</v>
+        <v>1961</v>
       </c>
       <c r="D969" t="s">
         <v>2802</v>
@@ -57631,11 +57691,11 @@
     </row>
     <row r="970" spans="1:5">
       <c r="A970" t="str">
-        <f t="shared" si="194"/>
+        <f t="shared" si="191"/>
         <v>A0F6</v>
       </c>
       <c r="B970" t="str">
-        <f t="shared" ref="B970" si="208">RIGHT(DEC2HEX(C970,4),2)&amp;LEFT(DEC2HEX(C970,4),2)</f>
+        <f t="shared" ref="B970:B974" si="206">RIGHT(DEC2HEX(C970,4),2)&amp;LEFT(DEC2HEX(C970,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C970">
@@ -57647,15 +57707,15 @@
     </row>
     <row r="971" spans="1:5">
       <c r="A971" t="str">
-        <f t="shared" si="194"/>
+        <f t="shared" si="191"/>
         <v>A0F8</v>
       </c>
       <c r="B971" t="str">
         <f>_xlfn.XLOOKUP(C971,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>F102</v>
+        <v>7A03</v>
       </c>
       <c r="C971" t="s">
-        <v>2218</v>
+        <v>3951</v>
       </c>
       <c r="D971" t="s">
         <v>2802</v>
@@ -57667,11 +57727,11 @@
     </row>
     <row r="972" spans="1:5">
       <c r="A972" t="str">
-        <f t="shared" ref="A969:A1000" si="209">DEC2HEX(HEX2DEC(A971)+LEN(B971)/2,4)</f>
+        <f t="shared" si="191"/>
         <v>A0FA</v>
       </c>
       <c r="B972" t="str">
-        <f t="shared" ref="B972" si="210">RIGHT(DEC2HEX(C972,4),2)&amp;LEFT(DEC2HEX(C972,4),2)</f>
+        <f t="shared" ref="B972" si="207">RIGHT(DEC2HEX(C972,4),2)&amp;LEFT(DEC2HEX(C972,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C972">
@@ -57683,15 +57743,15 @@
     </row>
     <row r="973" spans="1:5">
       <c r="A973" t="str">
-        <f t="shared" si="209"/>
+        <f t="shared" si="191"/>
         <v>A0FC</v>
       </c>
       <c r="B973" t="str">
         <f>_xlfn.XLOOKUP(C973,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>9E02</v>
+        <v>6803</v>
       </c>
       <c r="C973" t="s">
-        <v>1976</v>
+        <v>3940</v>
       </c>
       <c r="D973" t="s">
         <v>2802</v>
@@ -57703,11 +57763,11 @@
     </row>
     <row r="974" spans="1:5">
       <c r="A974" t="str">
-        <f t="shared" si="209"/>
+        <f t="shared" si="191"/>
         <v>A0FE</v>
       </c>
       <c r="B974" t="str">
-        <f t="shared" ref="B974" si="211">RIGHT(DEC2HEX(C974,4),2)&amp;LEFT(DEC2HEX(C974,4),2)</f>
+        <f t="shared" si="206"/>
         <v>1400</v>
       </c>
       <c r="C974">
@@ -57719,15 +57779,15 @@
     </row>
     <row r="975" spans="1:5">
       <c r="A975" t="str">
-        <f t="shared" ref="A975:A980" si="212">DEC2HEX(HEX2DEC(A974)+LEN(B974)/2,4)</f>
+        <f t="shared" si="191"/>
         <v>A100</v>
       </c>
       <c r="B975" t="str">
         <f>_xlfn.XLOOKUP(C975,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>F702</v>
+        <v>F602</v>
       </c>
       <c r="C975" t="s">
-        <v>2236</v>
+        <v>2233</v>
       </c>
       <c r="D975" t="s">
         <v>2802</v>
@@ -57739,11 +57799,11 @@
     </row>
     <row r="976" spans="1:5">
       <c r="A976" t="str">
-        <f t="shared" si="212"/>
+        <f t="shared" si="191"/>
         <v>A102</v>
       </c>
       <c r="B976" t="str">
-        <f t="shared" ref="B976" si="213">RIGHT(DEC2HEX(C976,4),2)&amp;LEFT(DEC2HEX(C976,4),2)</f>
+        <f t="shared" ref="B976" si="208">RIGHT(DEC2HEX(C976,4),2)&amp;LEFT(DEC2HEX(C976,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C976">
@@ -57755,15 +57815,15 @@
     </row>
     <row r="977" spans="1:5">
       <c r="A977" t="str">
-        <f t="shared" si="212"/>
+        <f t="shared" si="191"/>
         <v>A104</v>
       </c>
       <c r="B977" t="str">
         <f>_xlfn.XLOOKUP(C977,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>6503</v>
+        <v>9602</v>
       </c>
       <c r="C977" t="s">
-        <v>3901</v>
+        <v>1952</v>
       </c>
       <c r="D977" t="s">
         <v>2802</v>
@@ -57775,11 +57835,11 @@
     </row>
     <row r="978" spans="1:5">
       <c r="A978" t="str">
-        <f t="shared" si="212"/>
+        <f t="shared" si="191"/>
         <v>A106</v>
       </c>
       <c r="B978" t="str">
-        <f t="shared" ref="B978" si="214">RIGHT(DEC2HEX(C978,4),2)&amp;LEFT(DEC2HEX(C978,4),2)</f>
+        <f t="shared" ref="B978" si="209">RIGHT(DEC2HEX(C978,4),2)&amp;LEFT(DEC2HEX(C978,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C978">
@@ -57791,15 +57851,15 @@
     </row>
     <row r="979" spans="1:5">
       <c r="A979" t="str">
-        <f t="shared" si="212"/>
+        <f t="shared" si="191"/>
         <v>A108</v>
       </c>
       <c r="B979" t="str">
         <f>_xlfn.XLOOKUP(C979,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>F802</v>
+        <v>9702</v>
       </c>
       <c r="C979" t="s">
-        <v>2239</v>
+        <v>1955</v>
       </c>
       <c r="D979" t="s">
         <v>2802</v>
@@ -57811,11 +57871,11 @@
     </row>
     <row r="980" spans="1:5">
       <c r="A980" t="str">
-        <f t="shared" si="212"/>
+        <f t="shared" si="191"/>
         <v>A10A</v>
       </c>
       <c r="B980" t="str">
-        <f t="shared" ref="B980" si="215">RIGHT(DEC2HEX(C980,4),2)&amp;LEFT(DEC2HEX(C980,4),2)</f>
+        <f t="shared" ref="B980" si="210">RIGHT(DEC2HEX(C980,4),2)&amp;LEFT(DEC2HEX(C980,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C980">
@@ -57827,15 +57887,15 @@
     </row>
     <row r="981" spans="1:5">
       <c r="A981" t="str">
-        <f t="shared" si="209"/>
+        <f t="shared" si="191"/>
         <v>A10C</v>
       </c>
       <c r="B981" t="str">
         <f>_xlfn.XLOOKUP(C981,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>5D03</v>
+        <v>FA02</v>
       </c>
       <c r="C981" t="s">
-        <v>3876</v>
+        <v>2245</v>
       </c>
       <c r="D981" t="s">
         <v>2802</v>
@@ -57847,11 +57907,11 @@
     </row>
     <row r="982" spans="1:5">
       <c r="A982" t="str">
-        <f t="shared" si="209"/>
+        <f t="shared" si="191"/>
         <v>A10E</v>
       </c>
       <c r="B982" t="str">
-        <f t="shared" ref="B982" si="216">RIGHT(DEC2HEX(C982,4),2)&amp;LEFT(DEC2HEX(C982,4),2)</f>
+        <f t="shared" ref="B982" si="211">RIGHT(DEC2HEX(C982,4),2)&amp;LEFT(DEC2HEX(C982,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C982">
@@ -57863,15 +57923,15 @@
     </row>
     <row r="983" spans="1:5">
       <c r="A983" t="str">
-        <f t="shared" si="209"/>
+        <f t="shared" si="191"/>
         <v>A110</v>
       </c>
       <c r="B983" t="str">
         <f>_xlfn.XLOOKUP(C983,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>E100</v>
+        <v>9F02</v>
       </c>
       <c r="C983" t="s">
-        <v>660</v>
+        <v>1979</v>
       </c>
       <c r="D983" t="s">
         <v>2802</v>
@@ -57883,11 +57943,11 @@
     </row>
     <row r="984" spans="1:5">
       <c r="A984" t="str">
-        <f t="shared" si="209"/>
+        <f t="shared" si="191"/>
         <v>A112</v>
       </c>
       <c r="B984" t="str">
-        <f t="shared" ref="B984" si="217">RIGHT(DEC2HEX(C984,4),2)&amp;LEFT(DEC2HEX(C984,4),2)</f>
+        <f t="shared" ref="B984" si="212">RIGHT(DEC2HEX(C984,4),2)&amp;LEFT(DEC2HEX(C984,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C984">
@@ -57899,15 +57959,15 @@
     </row>
     <row r="985" spans="1:5">
       <c r="A985" t="str">
-        <f t="shared" si="209"/>
+        <f t="shared" si="191"/>
         <v>A114</v>
       </c>
       <c r="B985" t="str">
         <f>_xlfn.XLOOKUP(C985,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>F902</v>
+        <v>8203</v>
       </c>
       <c r="C985" t="s">
-        <v>2242</v>
+        <v>3960</v>
       </c>
       <c r="D985" t="s">
         <v>2802</v>
@@ -57919,11 +57979,11 @@
     </row>
     <row r="986" spans="1:5">
       <c r="A986" t="str">
-        <f t="shared" si="209"/>
+        <f t="shared" si="191"/>
         <v>A116</v>
       </c>
       <c r="B986" t="str">
-        <f t="shared" ref="B986" si="218">RIGHT(DEC2HEX(C986,4),2)&amp;LEFT(DEC2HEX(C986,4),2)</f>
+        <f t="shared" ref="B986" si="213">RIGHT(DEC2HEX(C986,4),2)&amp;LEFT(DEC2HEX(C986,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C986">
@@ -57935,15 +57995,15 @@
     </row>
     <row r="987" spans="1:5">
       <c r="A987" t="str">
-        <f t="shared" si="209"/>
+        <f t="shared" si="191"/>
         <v>A118</v>
       </c>
       <c r="B987" t="str">
         <f>_xlfn.XLOOKUP(C987,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>F002</v>
+        <v>6E03</v>
       </c>
       <c r="C987" t="s">
-        <v>2215</v>
+        <v>3953</v>
       </c>
       <c r="D987" t="s">
         <v>2802</v>
@@ -57955,11 +58015,11 @@
     </row>
     <row r="988" spans="1:5">
       <c r="A988" t="str">
-        <f t="shared" si="209"/>
+        <f t="shared" si="191"/>
         <v>A11A</v>
       </c>
       <c r="B988" t="str">
-        <f t="shared" ref="B988" si="219">RIGHT(DEC2HEX(C988,4),2)&amp;LEFT(DEC2HEX(C988,4),2)</f>
+        <f t="shared" ref="B988" si="214">RIGHT(DEC2HEX(C988,4),2)&amp;LEFT(DEC2HEX(C988,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C988">
@@ -57971,15 +58031,15 @@
     </row>
     <row r="989" spans="1:5">
       <c r="A989" t="str">
-        <f t="shared" si="209"/>
+        <f t="shared" si="191"/>
         <v>A11C</v>
       </c>
       <c r="B989" t="str">
         <f>_xlfn.XLOOKUP(C989,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>8100</v>
+        <v>7C03</v>
       </c>
       <c r="C989" t="s">
-        <v>3879</v>
+        <v>3954</v>
       </c>
       <c r="D989" t="s">
         <v>2802</v>
@@ -57991,11 +58051,11 @@
     </row>
     <row r="990" spans="1:5">
       <c r="A990" t="str">
-        <f t="shared" si="209"/>
+        <f t="shared" si="191"/>
         <v>A11E</v>
       </c>
       <c r="B990" t="str">
-        <f t="shared" ref="B990" si="220">RIGHT(DEC2HEX(C990,4),2)&amp;LEFT(DEC2HEX(C990,4),2)</f>
+        <f t="shared" ref="B990" si="215">RIGHT(DEC2HEX(C990,4),2)&amp;LEFT(DEC2HEX(C990,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C990">
@@ -58007,15 +58067,15 @@
     </row>
     <row r="991" spans="1:5">
       <c r="A991" t="str">
-        <f t="shared" si="209"/>
+        <f t="shared" si="191"/>
         <v>A120</v>
       </c>
       <c r="B991" t="str">
         <f>_xlfn.XLOOKUP(C991,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>9D02</v>
+        <v>6D03</v>
       </c>
       <c r="C991" t="s">
-        <v>1973</v>
+        <v>3945</v>
       </c>
       <c r="D991" t="s">
         <v>2802</v>
@@ -58027,11 +58087,11 @@
     </row>
     <row r="992" spans="1:5">
       <c r="A992" t="str">
-        <f t="shared" si="209"/>
+        <f t="shared" si="191"/>
         <v>A122</v>
       </c>
       <c r="B992" t="str">
-        <f t="shared" ref="B992" si="221">RIGHT(DEC2HEX(C992,4),2)&amp;LEFT(DEC2HEX(C992,4),2)</f>
+        <f t="shared" ref="B992" si="216">RIGHT(DEC2HEX(C992,4),2)&amp;LEFT(DEC2HEX(C992,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C992">
@@ -58043,15 +58103,15 @@
     </row>
     <row r="993" spans="1:5">
       <c r="A993" t="str">
-        <f t="shared" si="209"/>
+        <f t="shared" si="191"/>
         <v>A124</v>
       </c>
       <c r="B993" t="str">
         <f>_xlfn.XLOOKUP(C993,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>5F03</v>
+        <v>F202</v>
       </c>
       <c r="C993" t="s">
-        <v>3895</v>
+        <v>2221</v>
       </c>
       <c r="D993" t="s">
         <v>2802</v>
@@ -58063,11 +58123,11 @@
     </row>
     <row r="994" spans="1:5">
       <c r="A994" t="str">
-        <f t="shared" si="209"/>
+        <f t="shared" si="191"/>
         <v>A126</v>
       </c>
       <c r="B994" t="str">
-        <f t="shared" ref="B994" si="222">RIGHT(DEC2HEX(C994,4),2)&amp;LEFT(DEC2HEX(C994,4),2)</f>
+        <f t="shared" ref="B994" si="217">RIGHT(DEC2HEX(C994,4),2)&amp;LEFT(DEC2HEX(C994,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C994">
@@ -58079,15 +58139,15 @@
     </row>
     <row r="995" spans="1:5">
       <c r="A995" t="str">
-        <f t="shared" si="209"/>
+        <f t="shared" si="191"/>
         <v>A128</v>
       </c>
       <c r="B995" t="str">
         <f>_xlfn.XLOOKUP(C995,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>9302</v>
+        <v>0103</v>
       </c>
       <c r="C995" t="s">
-        <v>1943</v>
+        <v>2263</v>
       </c>
       <c r="D995" t="s">
         <v>2802</v>
@@ -58099,11 +58159,11 @@
     </row>
     <row r="996" spans="1:5">
       <c r="A996" t="str">
-        <f t="shared" si="209"/>
+        <f t="shared" si="191"/>
         <v>A12A</v>
       </c>
       <c r="B996" t="str">
-        <f t="shared" ref="B996" si="223">RIGHT(DEC2HEX(C996,4),2)&amp;LEFT(DEC2HEX(C996,4),2)</f>
+        <f t="shared" ref="B996" si="218">RIGHT(DEC2HEX(C996,4),2)&amp;LEFT(DEC2HEX(C996,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C996">
@@ -58115,15 +58175,15 @@
     </row>
     <row r="997" spans="1:5">
       <c r="A997" t="str">
-        <f t="shared" si="209"/>
+        <f t="shared" si="191"/>
         <v>A12C</v>
       </c>
       <c r="B997" t="str">
         <f>_xlfn.XLOOKUP(C997,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>4503</v>
+        <v>5E03</v>
       </c>
       <c r="C997" t="s">
-        <v>3885</v>
+        <v>3894</v>
       </c>
       <c r="D997" t="s">
         <v>2802</v>
@@ -58133,13 +58193,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="998" spans="1:5">
+    <row r="998" spans="1:5" ht="13.75" customHeight="1">
       <c r="A998" t="str">
-        <f t="shared" si="209"/>
+        <f t="shared" si="191"/>
         <v>A12E</v>
       </c>
       <c r="B998" t="str">
-        <f t="shared" ref="B998" si="224">RIGHT(DEC2HEX(C998,4),2)&amp;LEFT(DEC2HEX(C998,4),2)</f>
+        <f t="shared" ref="B998" si="219">RIGHT(DEC2HEX(C998,4),2)&amp;LEFT(DEC2HEX(C998,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C998">
@@ -58151,15 +58211,15 @@
     </row>
     <row r="999" spans="1:5">
       <c r="A999" t="str">
-        <f t="shared" si="209"/>
+        <f t="shared" si="191"/>
         <v>A130</v>
       </c>
       <c r="B999" t="str">
         <f>_xlfn.XLOOKUP(C999,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>8000</v>
+        <v>F102</v>
       </c>
       <c r="C999" t="s">
-        <v>3878</v>
+        <v>2218</v>
       </c>
       <c r="D999" t="s">
         <v>2802</v>
@@ -58171,11 +58231,11 @@
     </row>
     <row r="1000" spans="1:5">
       <c r="A1000" t="str">
-        <f t="shared" si="209"/>
+        <f t="shared" si="191"/>
         <v>A132</v>
       </c>
       <c r="B1000" t="str">
-        <f t="shared" ref="B1000" si="225">RIGHT(DEC2HEX(C1000,4),2)&amp;LEFT(DEC2HEX(C1000,4),2)</f>
+        <f t="shared" ref="B1000" si="220">RIGHT(DEC2HEX(C1000,4),2)&amp;LEFT(DEC2HEX(C1000,4),2)</f>
         <v>1400</v>
       </c>
       <c r="C1000">
@@ -58185,664 +58245,664 @@
         <v>2802</v>
       </c>
     </row>
+    <row r="1001" spans="1:5">
+      <c r="A1001" t="str">
+        <f t="shared" si="191"/>
+        <v>A134</v>
+      </c>
+      <c r="B1001" t="str">
+        <f>_xlfn.XLOOKUP(C1001,'table of items'!C:C,'table of items'!D:D)</f>
+        <v>9E02</v>
+      </c>
+      <c r="C1001" t="s">
+        <v>1976</v>
+      </c>
+      <c r="D1001" t="s">
+        <v>2802</v>
+      </c>
+      <c r="E1001">
+        <f>COUNTIF(C:C,"="&amp;C1001)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:5">
+      <c r="A1002" t="str">
+        <f t="shared" si="191"/>
+        <v>A136</v>
+      </c>
+      <c r="B1002" t="str">
+        <f t="shared" ref="B1002" si="221">RIGHT(DEC2HEX(C1002,4),2)&amp;LEFT(DEC2HEX(C1002,4),2)</f>
+        <v>1400</v>
+      </c>
+      <c r="C1002">
+        <v>20</v>
+      </c>
+      <c r="D1002" t="s">
+        <v>2802</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:5">
+      <c r="A1003" t="str">
+        <f t="shared" si="191"/>
+        <v>A138</v>
+      </c>
+      <c r="B1003" t="str">
+        <f>_xlfn.XLOOKUP(C1003,'table of items'!C:C,'table of items'!D:D)</f>
+        <v>8303</v>
+      </c>
+      <c r="C1003" t="s">
+        <v>3961</v>
+      </c>
+      <c r="D1003" t="s">
+        <v>2802</v>
+      </c>
+      <c r="E1003">
+        <f>COUNTIF(C:C,"="&amp;C1003)</f>
+        <v>1</v>
+      </c>
+    </row>
     <row r="1004" spans="1:5">
-      <c r="A1004" t="s">
-        <v>3875</v>
+      <c r="A1004" t="str">
+        <f t="shared" si="191"/>
+        <v>A13A</v>
       </c>
       <c r="B1004" t="str">
-        <f>_xlfn.XLOOKUP(C1004,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>5303</v>
-      </c>
-      <c r="C1004" t="s">
-        <v>2487</v>
+        <f t="shared" ref="B1004" si="222">RIGHT(DEC2HEX(C1004,4),2)&amp;LEFT(DEC2HEX(C1004,4),2)</f>
+        <v>1400</v>
+      </c>
+      <c r="C1004">
+        <v>20</v>
       </c>
       <c r="D1004" t="s">
-        <v>2803</v>
-      </c>
-      <c r="E1004">
-        <f>COUNTIF(C:C,"="&amp;C1004)</f>
-        <v>1</v>
+        <v>2802</v>
       </c>
     </row>
     <row r="1005" spans="1:5">
       <c r="A1005" t="str">
-        <f t="shared" ref="A1005:A1011" si="226">DEC2HEX(HEX2DEC(A1004)+LEN(B1004)/2,4)</f>
-        <v>9EBC</v>
+        <f t="shared" ref="A1005:A1036" si="223">DEC2HEX(HEX2DEC(A1004)+LEN(B1004)/2,4)</f>
+        <v>A13C</v>
       </c>
       <c r="B1005" t="str">
-        <f t="shared" ref="B1005" si="227">RIGHT(DEC2HEX(C1005,4),2)&amp;LEFT(DEC2HEX(C1005,4),2)</f>
-        <v>0100</v>
-      </c>
-      <c r="C1005">
+        <f>_xlfn.XLOOKUP(C1005,'table of items'!C:C,'table of items'!D:D)</f>
+        <v>8403</v>
+      </c>
+      <c r="C1005" t="s">
+        <v>3962</v>
+      </c>
+      <c r="D1005" t="s">
+        <v>2802</v>
+      </c>
+      <c r="E1005">
+        <f>COUNTIF(C:C,"="&amp;C1005)</f>
         <v>1</v>
-      </c>
-      <c r="D1005" t="s">
-        <v>2803</v>
       </c>
     </row>
     <row r="1006" spans="1:5">
       <c r="A1006" t="str">
-        <f t="shared" si="226"/>
-        <v>9EBE</v>
+        <f t="shared" si="223"/>
+        <v>A13E</v>
       </c>
       <c r="B1006" t="str">
-        <f>_xlfn.XLOOKUP(C1006,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>1000</v>
-      </c>
-      <c r="C1006" t="s">
-        <v>54</v>
+        <f t="shared" ref="B1006" si="224">RIGHT(DEC2HEX(C1006,4),2)&amp;LEFT(DEC2HEX(C1006,4),2)</f>
+        <v>1400</v>
+      </c>
+      <c r="C1006">
+        <v>20</v>
       </c>
       <c r="D1006" t="s">
-        <v>2803</v>
-      </c>
-      <c r="E1006">
-        <f>COUNTIF(C:C,"="&amp;C1006)</f>
-        <v>1</v>
+        <v>2802</v>
       </c>
     </row>
     <row r="1007" spans="1:5">
       <c r="A1007" t="str">
-        <f t="shared" si="226"/>
-        <v>9EC0</v>
+        <f t="shared" si="223"/>
+        <v>A140</v>
       </c>
       <c r="B1007" t="str">
-        <f t="shared" ref="B1007" si="228">RIGHT(DEC2HEX(C1007,4),2)&amp;LEFT(DEC2HEX(C1007,4),2)</f>
-        <v>0100</v>
-      </c>
-      <c r="C1007">
+        <f>_xlfn.XLOOKUP(C1007,'table of items'!C:C,'table of items'!D:D)</f>
+        <v>F702</v>
+      </c>
+      <c r="C1007" t="s">
+        <v>2236</v>
+      </c>
+      <c r="D1007" t="s">
+        <v>2802</v>
+      </c>
+      <c r="E1007">
+        <f>COUNTIF(C:C,"="&amp;C1007)</f>
         <v>1</v>
-      </c>
-      <c r="D1007" t="s">
-        <v>2803</v>
       </c>
     </row>
     <row r="1008" spans="1:5">
       <c r="A1008" t="str">
-        <f t="shared" si="226"/>
-        <v>9EC2</v>
+        <f t="shared" si="223"/>
+        <v>A142</v>
       </c>
       <c r="B1008" t="str">
-        <f>_xlfn.XLOOKUP(C1008,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>0700</v>
-      </c>
-      <c r="C1008" t="s">
-        <v>27</v>
+        <f t="shared" ref="B1008" si="225">RIGHT(DEC2HEX(C1008,4),2)&amp;LEFT(DEC2HEX(C1008,4),2)</f>
+        <v>1400</v>
+      </c>
+      <c r="C1008">
+        <v>20</v>
       </c>
       <c r="D1008" t="s">
-        <v>2803</v>
-      </c>
-      <c r="E1008">
-        <f>COUNTIF(C:C,"="&amp;C1008)</f>
-        <v>1</v>
+        <v>2802</v>
       </c>
     </row>
     <row r="1009" spans="1:5">
       <c r="A1009" t="str">
-        <f t="shared" si="226"/>
-        <v>9EC4</v>
+        <f t="shared" si="223"/>
+        <v>A144</v>
       </c>
       <c r="B1009" t="str">
-        <f t="shared" ref="B1009" si="229">RIGHT(DEC2HEX(C1009,4),2)&amp;LEFT(DEC2HEX(C1009,4),2)</f>
-        <v>0100</v>
-      </c>
-      <c r="C1009">
+        <f>_xlfn.XLOOKUP(C1009,'table of items'!C:C,'table of items'!D:D)</f>
+        <v>6503</v>
+      </c>
+      <c r="C1009" t="s">
+        <v>3901</v>
+      </c>
+      <c r="D1009" t="s">
+        <v>2802</v>
+      </c>
+      <c r="E1009">
+        <f>COUNTIF(C:C,"="&amp;C1009)</f>
         <v>1</v>
-      </c>
-      <c r="D1009" t="s">
-        <v>2803</v>
       </c>
     </row>
     <row r="1010" spans="1:5">
       <c r="A1010" t="str">
-        <f t="shared" si="226"/>
-        <v>9EC6</v>
+        <f t="shared" si="223"/>
+        <v>A146</v>
       </c>
       <c r="B1010" t="str">
-        <f>_xlfn.XLOOKUP(C1010,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>4002</v>
-      </c>
-      <c r="C1010" t="s">
-        <v>1698</v>
+        <f t="shared" ref="B1010" si="226">RIGHT(DEC2HEX(C1010,4),2)&amp;LEFT(DEC2HEX(C1010,4),2)</f>
+        <v>1400</v>
+      </c>
+      <c r="C1010">
+        <v>20</v>
       </c>
       <c r="D1010" t="s">
-        <v>2803</v>
-      </c>
-      <c r="E1010">
-        <f>COUNTIF(C:C,"="&amp;C1010)</f>
-        <v>1</v>
+        <v>2802</v>
       </c>
     </row>
     <row r="1011" spans="1:5">
       <c r="A1011" t="str">
-        <f t="shared" si="226"/>
-        <v>9EC8</v>
+        <f t="shared" si="223"/>
+        <v>A148</v>
       </c>
       <c r="B1011" t="str">
-        <f t="shared" ref="B1011" si="230">RIGHT(DEC2HEX(C1011,4),2)&amp;LEFT(DEC2HEX(C1011,4),2)</f>
-        <v>0100</v>
-      </c>
-      <c r="C1011">
+        <f>_xlfn.XLOOKUP(C1011,'table of items'!C:C,'table of items'!D:D)</f>
+        <v>F802</v>
+      </c>
+      <c r="C1011" t="s">
+        <v>2239</v>
+      </c>
+      <c r="D1011" t="s">
+        <v>2802</v>
+      </c>
+      <c r="E1011">
+        <f>COUNTIF(C:C,"="&amp;C1011)</f>
         <v>1</v>
-      </c>
-      <c r="D1011" t="s">
-        <v>2803</v>
       </c>
     </row>
     <row r="1012" spans="1:5">
       <c r="A1012" t="str">
-        <f t="shared" ref="A1012:A1045" si="231">DEC2HEX(HEX2DEC(A1011)+LEN(B1011)/2,4)</f>
-        <v>9ECA</v>
+        <f t="shared" si="223"/>
+        <v>A14A</v>
       </c>
       <c r="B1012" t="str">
-        <f>_xlfn.XLOOKUP(C1012,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>0D00</v>
-      </c>
-      <c r="C1012" t="s">
-        <v>45</v>
+        <f t="shared" ref="B1012" si="227">RIGHT(DEC2HEX(C1012,4),2)&amp;LEFT(DEC2HEX(C1012,4),2)</f>
+        <v>1400</v>
+      </c>
+      <c r="C1012">
+        <v>20</v>
       </c>
       <c r="D1012" t="s">
-        <v>2803</v>
-      </c>
-      <c r="E1012">
-        <f>COUNTIF(C:C,"="&amp;C1012)</f>
-        <v>1</v>
+        <v>2802</v>
       </c>
     </row>
     <row r="1013" spans="1:5">
       <c r="A1013" t="str">
-        <f t="shared" si="231"/>
-        <v>9ECC</v>
+        <f t="shared" si="223"/>
+        <v>A14C</v>
       </c>
       <c r="B1013" t="str">
-        <f t="shared" ref="B1013" si="232">RIGHT(DEC2HEX(C1013,4),2)&amp;LEFT(DEC2HEX(C1013,4),2)</f>
-        <v>0100</v>
-      </c>
-      <c r="C1013">
+        <f>_xlfn.XLOOKUP(C1013,'table of items'!C:C,'table of items'!D:D)</f>
+        <v>5D03</v>
+      </c>
+      <c r="C1013" t="s">
+        <v>3876</v>
+      </c>
+      <c r="D1013" t="s">
+        <v>2802</v>
+      </c>
+      <c r="E1013">
+        <f>COUNTIF(C:C,"="&amp;C1013)</f>
         <v>1</v>
-      </c>
-      <c r="D1013" t="s">
-        <v>2803</v>
       </c>
     </row>
     <row r="1014" spans="1:5">
       <c r="A1014" t="str">
-        <f t="shared" si="231"/>
-        <v>9ECE</v>
+        <f t="shared" si="223"/>
+        <v>A14E</v>
       </c>
       <c r="B1014" t="str">
-        <f>_xlfn.XLOOKUP(C1014,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>EC01</v>
-      </c>
-      <c r="C1014" t="s">
-        <v>1453</v>
+        <f t="shared" ref="B1014" si="228">RIGHT(DEC2HEX(C1014,4),2)&amp;LEFT(DEC2HEX(C1014,4),2)</f>
+        <v>1400</v>
+      </c>
+      <c r="C1014">
+        <v>20</v>
       </c>
       <c r="D1014" t="s">
-        <v>2803</v>
-      </c>
-      <c r="E1014">
-        <f>COUNTIF(C:C,"="&amp;C1014)</f>
-        <v>1</v>
+        <v>2802</v>
       </c>
     </row>
     <row r="1015" spans="1:5">
       <c r="A1015" t="str">
-        <f t="shared" si="231"/>
-        <v>9ED0</v>
+        <f t="shared" si="223"/>
+        <v>A150</v>
       </c>
       <c r="B1015" t="str">
-        <f t="shared" ref="B1015" si="233">RIGHT(DEC2HEX(C1015,4),2)&amp;LEFT(DEC2HEX(C1015,4),2)</f>
-        <v>0100</v>
-      </c>
-      <c r="C1015">
+        <f>_xlfn.XLOOKUP(C1015,'table of items'!C:C,'table of items'!D:D)</f>
+        <v>E100</v>
+      </c>
+      <c r="C1015" t="s">
+        <v>660</v>
+      </c>
+      <c r="D1015" t="s">
+        <v>2802</v>
+      </c>
+      <c r="E1015">
+        <f>COUNTIF(C:C,"="&amp;C1015)</f>
         <v>1</v>
-      </c>
-      <c r="D1015" t="s">
-        <v>2803</v>
       </c>
     </row>
     <row r="1016" spans="1:5">
       <c r="A1016" t="str">
-        <f t="shared" si="231"/>
-        <v>9ED2</v>
+        <f t="shared" si="223"/>
+        <v>A152</v>
       </c>
       <c r="B1016" t="str">
-        <f>_xlfn.XLOOKUP(C1016,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>F101</v>
-      </c>
-      <c r="C1016" t="s">
-        <v>1468</v>
+        <f t="shared" ref="B1016" si="229">RIGHT(DEC2HEX(C1016,4),2)&amp;LEFT(DEC2HEX(C1016,4),2)</f>
+        <v>1400</v>
+      </c>
+      <c r="C1016">
+        <v>20</v>
       </c>
       <c r="D1016" t="s">
-        <v>2803</v>
-      </c>
-      <c r="E1016">
-        <f>COUNTIF(C:C,"="&amp;C1016)</f>
-        <v>1</v>
+        <v>2802</v>
       </c>
     </row>
     <row r="1017" spans="1:5">
       <c r="A1017" t="str">
-        <f t="shared" si="231"/>
-        <v>9ED4</v>
+        <f t="shared" si="223"/>
+        <v>A154</v>
       </c>
       <c r="B1017" t="str">
-        <f t="shared" ref="B1017" si="234">RIGHT(DEC2HEX(C1017,4),2)&amp;LEFT(DEC2HEX(C1017,4),2)</f>
-        <v>0100</v>
-      </c>
-      <c r="C1017">
+        <f>_xlfn.XLOOKUP(C1017,'table of items'!C:C,'table of items'!D:D)</f>
+        <v>8503</v>
+      </c>
+      <c r="C1017" t="s">
+        <v>3963</v>
+      </c>
+      <c r="D1017" t="s">
+        <v>2802</v>
+      </c>
+      <c r="E1017">
+        <f>COUNTIF(C:C,"="&amp;C1017)</f>
         <v>1</v>
-      </c>
-      <c r="D1017" t="s">
-        <v>2803</v>
       </c>
     </row>
     <row r="1018" spans="1:5">
       <c r="A1018" t="str">
-        <f t="shared" si="231"/>
-        <v>9ED6</v>
+        <f t="shared" si="223"/>
+        <v>A156</v>
       </c>
       <c r="B1018" t="str">
-        <f>_xlfn.XLOOKUP(C1018,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>0E00</v>
-      </c>
-      <c r="C1018" t="s">
-        <v>48</v>
+        <f t="shared" ref="B1018" si="230">RIGHT(DEC2HEX(C1018,4),2)&amp;LEFT(DEC2HEX(C1018,4),2)</f>
+        <v>1400</v>
+      </c>
+      <c r="C1018">
+        <v>20</v>
       </c>
       <c r="D1018" t="s">
-        <v>2803</v>
-      </c>
-      <c r="E1018">
-        <f>COUNTIF(C:C,"="&amp;C1018)</f>
-        <v>1</v>
+        <v>2802</v>
       </c>
     </row>
     <row r="1019" spans="1:5">
       <c r="A1019" t="str">
-        <f t="shared" si="231"/>
-        <v>9ED8</v>
+        <f t="shared" si="223"/>
+        <v>A158</v>
       </c>
       <c r="B1019" t="str">
-        <f t="shared" ref="B1019" si="235">RIGHT(DEC2HEX(C1019,4),2)&amp;LEFT(DEC2HEX(C1019,4),2)</f>
-        <v>0100</v>
-      </c>
-      <c r="C1019">
+        <f>_xlfn.XLOOKUP(C1019,'table of items'!C:C,'table of items'!D:D)</f>
+        <v>7B03</v>
+      </c>
+      <c r="C1019" t="s">
+        <v>3952</v>
+      </c>
+      <c r="D1019" t="s">
+        <v>2802</v>
+      </c>
+      <c r="E1019">
+        <f>COUNTIF(C:C,"="&amp;C1019)</f>
         <v>1</v>
-      </c>
-      <c r="D1019" t="s">
-        <v>2803</v>
       </c>
     </row>
     <row r="1020" spans="1:5">
       <c r="A1020" t="str">
-        <f t="shared" si="231"/>
-        <v>9EDA</v>
+        <f t="shared" si="223"/>
+        <v>A15A</v>
       </c>
       <c r="B1020" t="str">
-        <f>_xlfn.XLOOKUP(C1020,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>EF01</v>
-      </c>
-      <c r="C1020" t="s">
-        <v>1462</v>
+        <f t="shared" ref="B1020" si="231">RIGHT(DEC2HEX(C1020,4),2)&amp;LEFT(DEC2HEX(C1020,4),2)</f>
+        <v>1400</v>
+      </c>
+      <c r="C1020">
+        <v>20</v>
       </c>
       <c r="D1020" t="s">
-        <v>2803</v>
-      </c>
-      <c r="E1020">
-        <f>COUNTIF(C:C,"="&amp;C1020)</f>
-        <v>1</v>
+        <v>2802</v>
       </c>
     </row>
     <row r="1021" spans="1:5">
       <c r="A1021" t="str">
-        <f t="shared" si="231"/>
-        <v>9EDC</v>
+        <f t="shared" si="223"/>
+        <v>A15C</v>
       </c>
       <c r="B1021" t="str">
-        <f t="shared" ref="B1021" si="236">RIGHT(DEC2HEX(C1021,4),2)&amp;LEFT(DEC2HEX(C1021,4),2)</f>
-        <v>0100</v>
-      </c>
-      <c r="C1021">
+        <f>_xlfn.XLOOKUP(C1021,'table of items'!C:C,'table of items'!D:D)</f>
+        <v>F902</v>
+      </c>
+      <c r="C1021" t="s">
+        <v>2242</v>
+      </c>
+      <c r="D1021" t="s">
+        <v>2802</v>
+      </c>
+      <c r="E1021">
+        <f>COUNTIF(C:C,"="&amp;C1021)</f>
         <v>1</v>
-      </c>
-      <c r="D1021" t="s">
-        <v>2803</v>
       </c>
     </row>
     <row r="1022" spans="1:5">
       <c r="A1022" t="str">
-        <f t="shared" si="231"/>
-        <v>9EDE</v>
+        <f t="shared" si="223"/>
+        <v>A15E</v>
       </c>
       <c r="B1022" t="str">
-        <f>_xlfn.XLOOKUP(C1022,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>ED01</v>
-      </c>
-      <c r="C1022" t="s">
-        <v>1456</v>
+        <f t="shared" ref="B1022" si="232">RIGHT(DEC2HEX(C1022,4),2)&amp;LEFT(DEC2HEX(C1022,4),2)</f>
+        <v>1400</v>
+      </c>
+      <c r="C1022">
+        <v>20</v>
       </c>
       <c r="D1022" t="s">
-        <v>2803</v>
-      </c>
-      <c r="E1022">
-        <f>COUNTIF(C:C,"="&amp;C1022)</f>
-        <v>1</v>
+        <v>2802</v>
       </c>
     </row>
     <row r="1023" spans="1:5">
       <c r="A1023" t="str">
-        <f t="shared" si="231"/>
-        <v>9EE0</v>
+        <f t="shared" si="223"/>
+        <v>A160</v>
       </c>
       <c r="B1023" t="str">
-        <f t="shared" ref="B1023" si="237">RIGHT(DEC2HEX(C1023,4),2)&amp;LEFT(DEC2HEX(C1023,4),2)</f>
-        <v>0100</v>
-      </c>
-      <c r="C1023">
+        <f>_xlfn.XLOOKUP(C1023,'table of items'!C:C,'table of items'!D:D)</f>
+        <v>F002</v>
+      </c>
+      <c r="C1023" t="s">
+        <v>2215</v>
+      </c>
+      <c r="D1023" t="s">
+        <v>2802</v>
+      </c>
+      <c r="E1023">
+        <f>COUNTIF(C:C,"="&amp;C1023)</f>
         <v>1</v>
-      </c>
-      <c r="D1023" t="s">
-        <v>2803</v>
       </c>
     </row>
     <row r="1024" spans="1:5">
       <c r="A1024" t="str">
-        <f t="shared" si="231"/>
-        <v>9EE2</v>
+        <f t="shared" si="223"/>
+        <v>A162</v>
       </c>
       <c r="B1024" t="str">
-        <f>_xlfn.XLOOKUP(C1024,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>F001</v>
-      </c>
-      <c r="C1024" t="s">
-        <v>1465</v>
+        <f t="shared" ref="B1024" si="233">RIGHT(DEC2HEX(C1024,4),2)&amp;LEFT(DEC2HEX(C1024,4),2)</f>
+        <v>1400</v>
+      </c>
+      <c r="C1024">
+        <v>20</v>
       </c>
       <c r="D1024" t="s">
-        <v>2803</v>
-      </c>
-      <c r="E1024">
-        <f>COUNTIF(C:C,"="&amp;C1024)</f>
-        <v>1</v>
+        <v>2802</v>
       </c>
     </row>
     <row r="1025" spans="1:5">
       <c r="A1025" t="str">
-        <f t="shared" si="231"/>
-        <v>9EE4</v>
+        <f t="shared" si="223"/>
+        <v>A164</v>
       </c>
       <c r="B1025" t="str">
-        <f t="shared" ref="B1025" si="238">RIGHT(DEC2HEX(C1025,4),2)&amp;LEFT(DEC2HEX(C1025,4),2)</f>
-        <v>0100</v>
-      </c>
-      <c r="C1025">
+        <f>_xlfn.XLOOKUP(C1025,'table of items'!C:C,'table of items'!D:D)</f>
+        <v>8100</v>
+      </c>
+      <c r="C1025" t="s">
+        <v>3879</v>
+      </c>
+      <c r="D1025" t="s">
+        <v>2802</v>
+      </c>
+      <c r="E1025">
+        <f>COUNTIF(C:C,"="&amp;C1025)</f>
         <v>1</v>
-      </c>
-      <c r="D1025" t="s">
-        <v>2803</v>
       </c>
     </row>
     <row r="1026" spans="1:5">
       <c r="A1026" t="str">
-        <f t="shared" si="231"/>
-        <v>9EE6</v>
+        <f t="shared" si="223"/>
+        <v>A166</v>
       </c>
       <c r="B1026" t="str">
-        <f>_xlfn.XLOOKUP(C1026,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>EE01</v>
-      </c>
-      <c r="C1026" t="s">
-        <v>1459</v>
+        <f t="shared" ref="B1026" si="234">RIGHT(DEC2HEX(C1026,4),2)&amp;LEFT(DEC2HEX(C1026,4),2)</f>
+        <v>1400</v>
+      </c>
+      <c r="C1026">
+        <v>20</v>
       </c>
       <c r="D1026" t="s">
-        <v>2803</v>
-      </c>
-      <c r="E1026">
-        <f>COUNTIF(C:C,"="&amp;C1026)</f>
-        <v>1</v>
+        <v>2802</v>
       </c>
     </row>
     <row r="1027" spans="1:5">
       <c r="A1027" t="str">
-        <f t="shared" si="231"/>
-        <v>9EE8</v>
+        <f t="shared" si="223"/>
+        <v>A168</v>
       </c>
       <c r="B1027" t="str">
-        <f t="shared" ref="B1027" si="239">RIGHT(DEC2HEX(C1027,4),2)&amp;LEFT(DEC2HEX(C1027,4),2)</f>
-        <v>0100</v>
-      </c>
-      <c r="C1027">
+        <f>_xlfn.XLOOKUP(C1027,'table of items'!C:C,'table of items'!D:D)</f>
+        <v>9D02</v>
+      </c>
+      <c r="C1027" t="s">
+        <v>1973</v>
+      </c>
+      <c r="D1027" t="s">
+        <v>2802</v>
+      </c>
+      <c r="E1027">
+        <f>COUNTIF(C:C,"="&amp;C1027)</f>
         <v>1</v>
-      </c>
-      <c r="D1027" t="s">
-        <v>2803</v>
       </c>
     </row>
     <row r="1028" spans="1:5">
       <c r="A1028" t="str">
-        <f t="shared" si="231"/>
-        <v>9EEA</v>
+        <f t="shared" si="223"/>
+        <v>A16A</v>
       </c>
       <c r="B1028" t="str">
-        <f>_xlfn.XLOOKUP(C1028,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>0B00</v>
-      </c>
-      <c r="C1028" t="s">
-        <v>39</v>
+        <f t="shared" ref="B1028" si="235">RIGHT(DEC2HEX(C1028,4),2)&amp;LEFT(DEC2HEX(C1028,4),2)</f>
+        <v>1400</v>
+      </c>
+      <c r="C1028">
+        <v>20</v>
       </c>
       <c r="D1028" t="s">
-        <v>2803</v>
-      </c>
-      <c r="E1028">
-        <f>COUNTIF(C:C,"="&amp;C1028)</f>
-        <v>1</v>
+        <v>2802</v>
       </c>
     </row>
     <row r="1029" spans="1:5">
       <c r="A1029" t="str">
-        <f t="shared" si="231"/>
-        <v>9EEC</v>
+        <f t="shared" si="223"/>
+        <v>A16C</v>
       </c>
       <c r="B1029" t="str">
-        <f t="shared" ref="B1029" si="240">RIGHT(DEC2HEX(C1029,4),2)&amp;LEFT(DEC2HEX(C1029,4),2)</f>
-        <v>0100</v>
-      </c>
-      <c r="C1029">
+        <f>_xlfn.XLOOKUP(C1029,'table of items'!C:C,'table of items'!D:D)</f>
+        <v>5F03</v>
+      </c>
+      <c r="C1029" t="s">
+        <v>3895</v>
+      </c>
+      <c r="D1029" t="s">
+        <v>2802</v>
+      </c>
+      <c r="E1029">
+        <f>COUNTIF(C:C,"="&amp;C1029)</f>
         <v>1</v>
-      </c>
-      <c r="D1029" t="s">
-        <v>2803</v>
       </c>
     </row>
     <row r="1030" spans="1:5">
       <c r="A1030" t="str">
-        <f t="shared" si="231"/>
-        <v>9EEE</v>
+        <f t="shared" si="223"/>
+        <v>A16E</v>
       </c>
       <c r="B1030" t="str">
-        <f>_xlfn.XLOOKUP(C1030,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>0100</v>
-      </c>
-      <c r="C1030" t="s">
-        <v>10</v>
+        <f t="shared" ref="B1030" si="236">RIGHT(DEC2HEX(C1030,4),2)&amp;LEFT(DEC2HEX(C1030,4),2)</f>
+        <v>1400</v>
+      </c>
+      <c r="C1030">
+        <v>20</v>
       </c>
       <c r="D1030" t="s">
-        <v>2803</v>
-      </c>
-      <c r="E1030">
-        <f>COUNTIF(C:C,"="&amp;C1030)</f>
-        <v>1</v>
+        <v>2802</v>
       </c>
     </row>
     <row r="1031" spans="1:5">
       <c r="A1031" t="str">
-        <f t="shared" si="231"/>
-        <v>9EF0</v>
+        <f t="shared" si="223"/>
+        <v>A170</v>
       </c>
       <c r="B1031" t="str">
-        <f t="shared" ref="B1031" si="241">RIGHT(DEC2HEX(C1031,4),2)&amp;LEFT(DEC2HEX(C1031,4),2)</f>
-        <v>6400</v>
-      </c>
-      <c r="C1031">
-        <v>100</v>
+        <f>_xlfn.XLOOKUP(C1031,'table of items'!C:C,'table of items'!D:D)</f>
+        <v>9302</v>
+      </c>
+      <c r="C1031" t="s">
+        <v>1943</v>
       </c>
       <c r="D1031" t="s">
-        <v>2803</v>
+        <v>2802</v>
+      </c>
+      <c r="E1031">
+        <f>COUNTIF(C:C,"="&amp;C1031)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1032" spans="1:5">
       <c r="A1032" t="str">
-        <f t="shared" si="231"/>
-        <v>9EF2</v>
+        <f t="shared" si="223"/>
+        <v>A172</v>
       </c>
       <c r="B1032" t="str">
-        <f>_xlfn.XLOOKUP(C1032,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>F201</v>
-      </c>
-      <c r="C1032" t="s">
-        <v>1471</v>
+        <f t="shared" ref="B1032" si="237">RIGHT(DEC2HEX(C1032,4),2)&amp;LEFT(DEC2HEX(C1032,4),2)</f>
+        <v>1400</v>
+      </c>
+      <c r="C1032">
+        <v>20</v>
       </c>
       <c r="D1032" t="s">
-        <v>2803</v>
-      </c>
-      <c r="E1032">
-        <f>COUNTIF(C:C,"="&amp;C1032)</f>
-        <v>1</v>
+        <v>2802</v>
       </c>
     </row>
     <row r="1033" spans="1:5">
       <c r="A1033" t="str">
-        <f t="shared" si="231"/>
-        <v>9EF4</v>
+        <f t="shared" si="223"/>
+        <v>A174</v>
       </c>
       <c r="B1033" t="str">
-        <f t="shared" ref="B1033" si="242">RIGHT(DEC2HEX(C1033,4),2)&amp;LEFT(DEC2HEX(C1033,4),2)</f>
-        <v>0100</v>
-      </c>
-      <c r="C1033">
+        <f>_xlfn.XLOOKUP(C1033,'table of items'!C:C,'table of items'!D:D)</f>
+        <v>4503</v>
+      </c>
+      <c r="C1033" t="s">
+        <v>3885</v>
+      </c>
+      <c r="D1033" t="s">
+        <v>2802</v>
+      </c>
+      <c r="E1033">
+        <f>COUNTIF(C:C,"="&amp;C1033)</f>
         <v>1</v>
-      </c>
-      <c r="D1033" t="s">
-        <v>2803</v>
       </c>
     </row>
     <row r="1034" spans="1:5">
       <c r="A1034" t="str">
-        <f t="shared" si="231"/>
-        <v>9EF6</v>
+        <f t="shared" si="223"/>
+        <v>A176</v>
       </c>
       <c r="B1034" t="str">
-        <f>_xlfn.XLOOKUP(C1034,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>0800</v>
-      </c>
-      <c r="C1034" t="s">
-        <v>30</v>
+        <f t="shared" ref="B1034" si="238">RIGHT(DEC2HEX(C1034,4),2)&amp;LEFT(DEC2HEX(C1034,4),2)</f>
+        <v>1400</v>
+      </c>
+      <c r="C1034">
+        <v>20</v>
       </c>
       <c r="D1034" t="s">
-        <v>2803</v>
-      </c>
-      <c r="E1034">
-        <f>COUNTIF(C:C,"="&amp;C1034)</f>
-        <v>1</v>
+        <v>2802</v>
       </c>
     </row>
     <row r="1035" spans="1:5">
       <c r="A1035" t="str">
-        <f t="shared" si="231"/>
-        <v>9EF8</v>
+        <f t="shared" si="223"/>
+        <v>A178</v>
       </c>
       <c r="B1035" t="str">
-        <f t="shared" ref="B1035" si="243">RIGHT(DEC2HEX(C1035,4),2)&amp;LEFT(DEC2HEX(C1035,4),2)</f>
-        <v>0100</v>
-      </c>
-      <c r="C1035">
+        <f>_xlfn.XLOOKUP(C1035,'table of items'!C:C,'table of items'!D:D)</f>
+        <v>8000</v>
+      </c>
+      <c r="C1035" t="s">
+        <v>3878</v>
+      </c>
+      <c r="D1035" t="s">
+        <v>2802</v>
+      </c>
+      <c r="E1035">
+        <f>COUNTIF(C:C,"="&amp;C1035)</f>
         <v>1</v>
-      </c>
-      <c r="D1035" t="s">
-        <v>2803</v>
       </c>
     </row>
     <row r="1036" spans="1:5">
       <c r="A1036" t="str">
-        <f t="shared" si="231"/>
-        <v>9EFA</v>
+        <f t="shared" si="223"/>
+        <v>A17A</v>
       </c>
       <c r="B1036" t="str">
-        <f>_xlfn.XLOOKUP(C1036,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>F401</v>
-      </c>
-      <c r="C1036" t="s">
-        <v>1477</v>
+        <f t="shared" ref="B1036" si="239">RIGHT(DEC2HEX(C1036,4),2)&amp;LEFT(DEC2HEX(C1036,4),2)</f>
+        <v>1400</v>
+      </c>
+      <c r="C1036">
+        <v>20</v>
       </c>
       <c r="D1036" t="s">
-        <v>2803</v>
-      </c>
-      <c r="E1036">
-        <f>COUNTIF(C:C,"="&amp;C1036)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="1037" spans="1:5">
-      <c r="A1037" t="str">
-        <f t="shared" si="231"/>
-        <v>9EFC</v>
-      </c>
-      <c r="B1037" t="str">
-        <f t="shared" ref="B1037" si="244">RIGHT(DEC2HEX(C1037,4),2)&amp;LEFT(DEC2HEX(C1037,4),2)</f>
-        <v>0100</v>
-      </c>
-      <c r="C1037">
-        <v>1</v>
-      </c>
-      <c r="D1037" t="s">
-        <v>2803</v>
-      </c>
-    </row>
-    <row r="1038" spans="1:5">
-      <c r="A1038" t="str">
-        <f t="shared" si="231"/>
-        <v>9EFE</v>
-      </c>
-      <c r="B1038" t="str">
-        <f>_xlfn.XLOOKUP(C1038,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>0F00</v>
-      </c>
-      <c r="C1038" t="s">
-        <v>51</v>
-      </c>
-      <c r="D1038" t="s">
-        <v>2803</v>
-      </c>
-      <c r="E1038">
-        <f>COUNTIF(C:C,"="&amp;C1038)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="1039" spans="1:5">
-      <c r="A1039" t="str">
-        <f t="shared" si="231"/>
-        <v>9F00</v>
-      </c>
-      <c r="B1039" t="str">
-        <f t="shared" ref="B1039" si="245">RIGHT(DEC2HEX(C1039,4),2)&amp;LEFT(DEC2HEX(C1039,4),2)</f>
-        <v>0100</v>
-      </c>
-      <c r="C1039">
-        <v>1</v>
-      </c>
-      <c r="D1039" t="s">
-        <v>2803</v>
+        <v>2802</v>
       </c>
     </row>
     <row r="1040" spans="1:5">
-      <c r="A1040" t="str">
-        <f t="shared" si="231"/>
-        <v>9F02</v>
+      <c r="A1040" t="s">
+        <v>3875</v>
       </c>
       <c r="B1040" t="str">
         <f>_xlfn.XLOOKUP(C1040,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>0500</v>
+        <v>5303</v>
       </c>
       <c r="C1040" t="s">
-        <v>21</v>
+        <v>2487</v>
       </c>
       <c r="D1040" t="s">
         <v>2803</v>
@@ -58854,11 +58914,11 @@
     </row>
     <row r="1041" spans="1:5">
       <c r="A1041" t="str">
-        <f t="shared" si="231"/>
-        <v>9F04</v>
+        <f t="shared" ref="A1041:A1047" si="240">DEC2HEX(HEX2DEC(A1040)+LEN(B1040)/2,4)</f>
+        <v>9EBC</v>
       </c>
       <c r="B1041" t="str">
-        <f t="shared" ref="B1041" si="246">RIGHT(DEC2HEX(C1041,4),2)&amp;LEFT(DEC2HEX(C1041,4),2)</f>
+        <f t="shared" ref="B1041" si="241">RIGHT(DEC2HEX(C1041,4),2)&amp;LEFT(DEC2HEX(C1041,4),2)</f>
         <v>0100</v>
       </c>
       <c r="C1041">
@@ -58870,15 +58930,15 @@
     </row>
     <row r="1042" spans="1:5">
       <c r="A1042" t="str">
-        <f t="shared" si="231"/>
-        <v>9F06</v>
+        <f t="shared" si="240"/>
+        <v>9EBE</v>
       </c>
       <c r="B1042" t="str">
         <f>_xlfn.XLOOKUP(C1042,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>F301</v>
+        <v>1000</v>
       </c>
       <c r="C1042" t="s">
-        <v>1474</v>
+        <v>54</v>
       </c>
       <c r="D1042" t="s">
         <v>2803</v>
@@ -58890,11 +58950,11 @@
     </row>
     <row r="1043" spans="1:5">
       <c r="A1043" t="str">
-        <f t="shared" si="231"/>
-        <v>9F08</v>
+        <f t="shared" si="240"/>
+        <v>9EC0</v>
       </c>
       <c r="B1043" t="str">
-        <f t="shared" ref="B1043" si="247">RIGHT(DEC2HEX(C1043,4),2)&amp;LEFT(DEC2HEX(C1043,4),2)</f>
+        <f t="shared" ref="B1043" si="242">RIGHT(DEC2HEX(C1043,4),2)&amp;LEFT(DEC2HEX(C1043,4),2)</f>
         <v>0100</v>
       </c>
       <c r="C1043">
@@ -58906,15 +58966,15 @@
     </row>
     <row r="1044" spans="1:5">
       <c r="A1044" t="str">
-        <f t="shared" si="231"/>
-        <v>9F0A</v>
+        <f t="shared" si="240"/>
+        <v>9EC2</v>
       </c>
       <c r="B1044" t="str">
         <f>_xlfn.XLOOKUP(C1044,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>0A00</v>
+        <v>0700</v>
       </c>
       <c r="C1044" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D1044" t="s">
         <v>2803</v>
@@ -58926,11 +58986,11 @@
     </row>
     <row r="1045" spans="1:5">
       <c r="A1045" t="str">
-        <f t="shared" si="231"/>
-        <v>9F0C</v>
+        <f t="shared" si="240"/>
+        <v>9EC4</v>
       </c>
       <c r="B1045" t="str">
-        <f t="shared" ref="B1045" si="248">RIGHT(DEC2HEX(C1045,4),2)&amp;LEFT(DEC2HEX(C1045,4),2)</f>
+        <f t="shared" ref="B1045" si="243">RIGHT(DEC2HEX(C1045,4),2)&amp;LEFT(DEC2HEX(C1045,4),2)</f>
         <v>0100</v>
       </c>
       <c r="C1045">
@@ -58942,15 +59002,15 @@
     </row>
     <row r="1046" spans="1:5">
       <c r="A1046" t="str">
-        <f t="shared" ref="A1046:A1047" si="249">DEC2HEX(HEX2DEC(A1045)+LEN(B1045)/2,4)</f>
-        <v>9F0E</v>
+        <f t="shared" si="240"/>
+        <v>9EC6</v>
       </c>
       <c r="B1046" t="str">
         <f>_xlfn.XLOOKUP(C1046,'table of items'!C:C,'table of items'!D:D)</f>
-        <v>7E00</v>
+        <v>4002</v>
       </c>
       <c r="C1046" t="s">
-        <v>3874</v>
+        <v>1698</v>
       </c>
       <c r="D1046" t="s">
         <v>2803</v>
@@ -58962,23 +59022,671 @@
     </row>
     <row r="1047" spans="1:5">
       <c r="A1047" t="str">
-        <f t="shared" si="249"/>
-        <v>9F10</v>
+        <f t="shared" si="240"/>
+        <v>9EC8</v>
       </c>
       <c r="B1047" t="str">
-        <f t="shared" ref="B1047" si="250">RIGHT(DEC2HEX(C1047,4),2)&amp;LEFT(DEC2HEX(C1047,4),2)</f>
-        <v>0F00</v>
+        <f t="shared" ref="B1047" si="244">RIGHT(DEC2HEX(C1047,4),2)&amp;LEFT(DEC2HEX(C1047,4),2)</f>
+        <v>0100</v>
       </c>
       <c r="C1047">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D1047" t="s">
         <v>2803</v>
       </c>
     </row>
+    <row r="1048" spans="1:5">
+      <c r="A1048" t="str">
+        <f t="shared" ref="A1048:A1081" si="245">DEC2HEX(HEX2DEC(A1047)+LEN(B1047)/2,4)</f>
+        <v>9ECA</v>
+      </c>
+      <c r="B1048" t="str">
+        <f>_xlfn.XLOOKUP(C1048,'table of items'!C:C,'table of items'!D:D)</f>
+        <v>0D00</v>
+      </c>
+      <c r="C1048" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1048" t="s">
+        <v>2803</v>
+      </c>
+      <c r="E1048">
+        <f>COUNTIF(C:C,"="&amp;C1048)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:5">
+      <c r="A1049" t="str">
+        <f t="shared" si="245"/>
+        <v>9ECC</v>
+      </c>
+      <c r="B1049" t="str">
+        <f t="shared" ref="B1049" si="246">RIGHT(DEC2HEX(C1049,4),2)&amp;LEFT(DEC2HEX(C1049,4),2)</f>
+        <v>0100</v>
+      </c>
+      <c r="C1049">
+        <v>1</v>
+      </c>
+      <c r="D1049" t="s">
+        <v>2803</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:5">
+      <c r="A1050" t="str">
+        <f t="shared" si="245"/>
+        <v>9ECE</v>
+      </c>
+      <c r="B1050" t="str">
+        <f>_xlfn.XLOOKUP(C1050,'table of items'!C:C,'table of items'!D:D)</f>
+        <v>EC01</v>
+      </c>
+      <c r="C1050" t="s">
+        <v>1453</v>
+      </c>
+      <c r="D1050" t="s">
+        <v>2803</v>
+      </c>
+      <c r="E1050">
+        <f>COUNTIF(C:C,"="&amp;C1050)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:5">
+      <c r="A1051" t="str">
+        <f t="shared" si="245"/>
+        <v>9ED0</v>
+      </c>
+      <c r="B1051" t="str">
+        <f t="shared" ref="B1051" si="247">RIGHT(DEC2HEX(C1051,4),2)&amp;LEFT(DEC2HEX(C1051,4),2)</f>
+        <v>0100</v>
+      </c>
+      <c r="C1051">
+        <v>1</v>
+      </c>
+      <c r="D1051" t="s">
+        <v>2803</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:5">
+      <c r="A1052" t="str">
+        <f t="shared" si="245"/>
+        <v>9ED2</v>
+      </c>
+      <c r="B1052" t="str">
+        <f>_xlfn.XLOOKUP(C1052,'table of items'!C:C,'table of items'!D:D)</f>
+        <v>F101</v>
+      </c>
+      <c r="C1052" t="s">
+        <v>1468</v>
+      </c>
+      <c r="D1052" t="s">
+        <v>2803</v>
+      </c>
+      <c r="E1052">
+        <f>COUNTIF(C:C,"="&amp;C1052)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:5">
+      <c r="A1053" t="str">
+        <f t="shared" si="245"/>
+        <v>9ED4</v>
+      </c>
+      <c r="B1053" t="str">
+        <f t="shared" ref="B1053" si="248">RIGHT(DEC2HEX(C1053,4),2)&amp;LEFT(DEC2HEX(C1053,4),2)</f>
+        <v>0100</v>
+      </c>
+      <c r="C1053">
+        <v>1</v>
+      </c>
+      <c r="D1053" t="s">
+        <v>2803</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:5">
+      <c r="A1054" t="str">
+        <f t="shared" si="245"/>
+        <v>9ED6</v>
+      </c>
+      <c r="B1054" t="str">
+        <f>_xlfn.XLOOKUP(C1054,'table of items'!C:C,'table of items'!D:D)</f>
+        <v>0E00</v>
+      </c>
+      <c r="C1054" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1054" t="s">
+        <v>2803</v>
+      </c>
+      <c r="E1054">
+        <f>COUNTIF(C:C,"="&amp;C1054)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:5">
+      <c r="A1055" t="str">
+        <f t="shared" si="245"/>
+        <v>9ED8</v>
+      </c>
+      <c r="B1055" t="str">
+        <f t="shared" ref="B1055" si="249">RIGHT(DEC2HEX(C1055,4),2)&amp;LEFT(DEC2HEX(C1055,4),2)</f>
+        <v>0100</v>
+      </c>
+      <c r="C1055">
+        <v>1</v>
+      </c>
+      <c r="D1055" t="s">
+        <v>2803</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:5">
+      <c r="A1056" t="str">
+        <f t="shared" si="245"/>
+        <v>9EDA</v>
+      </c>
+      <c r="B1056" t="str">
+        <f>_xlfn.XLOOKUP(C1056,'table of items'!C:C,'table of items'!D:D)</f>
+        <v>EF01</v>
+      </c>
+      <c r="C1056" t="s">
+        <v>1462</v>
+      </c>
+      <c r="D1056" t="s">
+        <v>2803</v>
+      </c>
+      <c r="E1056">
+        <f>COUNTIF(C:C,"="&amp;C1056)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:5">
+      <c r="A1057" t="str">
+        <f t="shared" si="245"/>
+        <v>9EDC</v>
+      </c>
+      <c r="B1057" t="str">
+        <f t="shared" ref="B1057" si="250">RIGHT(DEC2HEX(C1057,4),2)&amp;LEFT(DEC2HEX(C1057,4),2)</f>
+        <v>0100</v>
+      </c>
+      <c r="C1057">
+        <v>1</v>
+      </c>
+      <c r="D1057" t="s">
+        <v>2803</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:5">
+      <c r="A1058" t="str">
+        <f t="shared" si="245"/>
+        <v>9EDE</v>
+      </c>
+      <c r="B1058" t="str">
+        <f>_xlfn.XLOOKUP(C1058,'table of items'!C:C,'table of items'!D:D)</f>
+        <v>ED01</v>
+      </c>
+      <c r="C1058" t="s">
+        <v>1456</v>
+      </c>
+      <c r="D1058" t="s">
+        <v>2803</v>
+      </c>
+      <c r="E1058">
+        <f>COUNTIF(C:C,"="&amp;C1058)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:5">
+      <c r="A1059" t="str">
+        <f t="shared" si="245"/>
+        <v>9EE0</v>
+      </c>
+      <c r="B1059" t="str">
+        <f t="shared" ref="B1059" si="251">RIGHT(DEC2HEX(C1059,4),2)&amp;LEFT(DEC2HEX(C1059,4),2)</f>
+        <v>0100</v>
+      </c>
+      <c r="C1059">
+        <v>1</v>
+      </c>
+      <c r="D1059" t="s">
+        <v>2803</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:5">
+      <c r="A1060" t="str">
+        <f t="shared" si="245"/>
+        <v>9EE2</v>
+      </c>
+      <c r="B1060" t="str">
+        <f>_xlfn.XLOOKUP(C1060,'table of items'!C:C,'table of items'!D:D)</f>
+        <v>F001</v>
+      </c>
+      <c r="C1060" t="s">
+        <v>1465</v>
+      </c>
+      <c r="D1060" t="s">
+        <v>2803</v>
+      </c>
+      <c r="E1060">
+        <f>COUNTIF(C:C,"="&amp;C1060)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:5">
+      <c r="A1061" t="str">
+        <f t="shared" si="245"/>
+        <v>9EE4</v>
+      </c>
+      <c r="B1061" t="str">
+        <f t="shared" ref="B1061" si="252">RIGHT(DEC2HEX(C1061,4),2)&amp;LEFT(DEC2HEX(C1061,4),2)</f>
+        <v>0100</v>
+      </c>
+      <c r="C1061">
+        <v>1</v>
+      </c>
+      <c r="D1061" t="s">
+        <v>2803</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:5">
+      <c r="A1062" t="str">
+        <f t="shared" si="245"/>
+        <v>9EE6</v>
+      </c>
+      <c r="B1062" t="str">
+        <f>_xlfn.XLOOKUP(C1062,'table of items'!C:C,'table of items'!D:D)</f>
+        <v>EE01</v>
+      </c>
+      <c r="C1062" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D1062" t="s">
+        <v>2803</v>
+      </c>
+      <c r="E1062">
+        <f>COUNTIF(C:C,"="&amp;C1062)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:5">
+      <c r="A1063" t="str">
+        <f t="shared" si="245"/>
+        <v>9EE8</v>
+      </c>
+      <c r="B1063" t="str">
+        <f t="shared" ref="B1063" si="253">RIGHT(DEC2HEX(C1063,4),2)&amp;LEFT(DEC2HEX(C1063,4),2)</f>
+        <v>0100</v>
+      </c>
+      <c r="C1063">
+        <v>1</v>
+      </c>
+      <c r="D1063" t="s">
+        <v>2803</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:5">
+      <c r="A1064" t="str">
+        <f t="shared" si="245"/>
+        <v>9EEA</v>
+      </c>
+      <c r="B1064" t="str">
+        <f>_xlfn.XLOOKUP(C1064,'table of items'!C:C,'table of items'!D:D)</f>
+        <v>0B00</v>
+      </c>
+      <c r="C1064" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1064" t="s">
+        <v>2803</v>
+      </c>
+      <c r="E1064">
+        <f>COUNTIF(C:C,"="&amp;C1064)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:5">
+      <c r="A1065" t="str">
+        <f t="shared" si="245"/>
+        <v>9EEC</v>
+      </c>
+      <c r="B1065" t="str">
+        <f t="shared" ref="B1065" si="254">RIGHT(DEC2HEX(C1065,4),2)&amp;LEFT(DEC2HEX(C1065,4),2)</f>
+        <v>0100</v>
+      </c>
+      <c r="C1065">
+        <v>1</v>
+      </c>
+      <c r="D1065" t="s">
+        <v>2803</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:5">
+      <c r="A1066" t="str">
+        <f t="shared" si="245"/>
+        <v>9EEE</v>
+      </c>
+      <c r="B1066" t="str">
+        <f>_xlfn.XLOOKUP(C1066,'table of items'!C:C,'table of items'!D:D)</f>
+        <v>0100</v>
+      </c>
+      <c r="C1066" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1066" t="s">
+        <v>2803</v>
+      </c>
+      <c r="E1066">
+        <f>COUNTIF(C:C,"="&amp;C1066)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:5">
+      <c r="A1067" t="str">
+        <f t="shared" si="245"/>
+        <v>9EF0</v>
+      </c>
+      <c r="B1067" t="str">
+        <f t="shared" ref="B1067" si="255">RIGHT(DEC2HEX(C1067,4),2)&amp;LEFT(DEC2HEX(C1067,4),2)</f>
+        <v>6400</v>
+      </c>
+      <c r="C1067">
+        <v>100</v>
+      </c>
+      <c r="D1067" t="s">
+        <v>2803</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:5">
+      <c r="A1068" t="str">
+        <f t="shared" si="245"/>
+        <v>9EF2</v>
+      </c>
+      <c r="B1068" t="str">
+        <f>_xlfn.XLOOKUP(C1068,'table of items'!C:C,'table of items'!D:D)</f>
+        <v>F201</v>
+      </c>
+      <c r="C1068" t="s">
+        <v>1471</v>
+      </c>
+      <c r="D1068" t="s">
+        <v>2803</v>
+      </c>
+      <c r="E1068">
+        <f>COUNTIF(C:C,"="&amp;C1068)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:5">
+      <c r="A1069" t="str">
+        <f t="shared" si="245"/>
+        <v>9EF4</v>
+      </c>
+      <c r="B1069" t="str">
+        <f t="shared" ref="B1069" si="256">RIGHT(DEC2HEX(C1069,4),2)&amp;LEFT(DEC2HEX(C1069,4),2)</f>
+        <v>0100</v>
+      </c>
+      <c r="C1069">
+        <v>1</v>
+      </c>
+      <c r="D1069" t="s">
+        <v>2803</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:5">
+      <c r="A1070" t="str">
+        <f t="shared" si="245"/>
+        <v>9EF6</v>
+      </c>
+      <c r="B1070" t="str">
+        <f>_xlfn.XLOOKUP(C1070,'table of items'!C:C,'table of items'!D:D)</f>
+        <v>0800</v>
+      </c>
+      <c r="C1070" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1070" t="s">
+        <v>2803</v>
+      </c>
+      <c r="E1070">
+        <f>COUNTIF(C:C,"="&amp;C1070)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:5">
+      <c r="A1071" t="str">
+        <f t="shared" si="245"/>
+        <v>9EF8</v>
+      </c>
+      <c r="B1071" t="str">
+        <f t="shared" ref="B1071" si="257">RIGHT(DEC2HEX(C1071,4),2)&amp;LEFT(DEC2HEX(C1071,4),2)</f>
+        <v>0100</v>
+      </c>
+      <c r="C1071">
+        <v>1</v>
+      </c>
+      <c r="D1071" t="s">
+        <v>2803</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:5">
+      <c r="A1072" t="str">
+        <f t="shared" si="245"/>
+        <v>9EFA</v>
+      </c>
+      <c r="B1072" t="str">
+        <f>_xlfn.XLOOKUP(C1072,'table of items'!C:C,'table of items'!D:D)</f>
+        <v>F401</v>
+      </c>
+      <c r="C1072" t="s">
+        <v>1477</v>
+      </c>
+      <c r="D1072" t="s">
+        <v>2803</v>
+      </c>
+      <c r="E1072">
+        <f>COUNTIF(C:C,"="&amp;C1072)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:5">
+      <c r="A1073" t="str">
+        <f t="shared" si="245"/>
+        <v>9EFC</v>
+      </c>
+      <c r="B1073" t="str">
+        <f t="shared" ref="B1073" si="258">RIGHT(DEC2HEX(C1073,4),2)&amp;LEFT(DEC2HEX(C1073,4),2)</f>
+        <v>0100</v>
+      </c>
+      <c r="C1073">
+        <v>1</v>
+      </c>
+      <c r="D1073" t="s">
+        <v>2803</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:5">
+      <c r="A1074" t="str">
+        <f t="shared" si="245"/>
+        <v>9EFE</v>
+      </c>
+      <c r="B1074" t="str">
+        <f>_xlfn.XLOOKUP(C1074,'table of items'!C:C,'table of items'!D:D)</f>
+        <v>0F00</v>
+      </c>
+      <c r="C1074" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1074" t="s">
+        <v>2803</v>
+      </c>
+      <c r="E1074">
+        <f>COUNTIF(C:C,"="&amp;C1074)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:5">
+      <c r="A1075" t="str">
+        <f t="shared" si="245"/>
+        <v>9F00</v>
+      </c>
+      <c r="B1075" t="str">
+        <f t="shared" ref="B1075" si="259">RIGHT(DEC2HEX(C1075,4),2)&amp;LEFT(DEC2HEX(C1075,4),2)</f>
+        <v>0100</v>
+      </c>
+      <c r="C1075">
+        <v>1</v>
+      </c>
+      <c r="D1075" t="s">
+        <v>2803</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:5">
+      <c r="A1076" t="str">
+        <f t="shared" si="245"/>
+        <v>9F02</v>
+      </c>
+      <c r="B1076" t="str">
+        <f>_xlfn.XLOOKUP(C1076,'table of items'!C:C,'table of items'!D:D)</f>
+        <v>0500</v>
+      </c>
+      <c r="C1076" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1076" t="s">
+        <v>2803</v>
+      </c>
+      <c r="E1076">
+        <f>COUNTIF(C:C,"="&amp;C1076)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:5">
+      <c r="A1077" t="str">
+        <f t="shared" si="245"/>
+        <v>9F04</v>
+      </c>
+      <c r="B1077" t="str">
+        <f t="shared" ref="B1077" si="260">RIGHT(DEC2HEX(C1077,4),2)&amp;LEFT(DEC2HEX(C1077,4),2)</f>
+        <v>0100</v>
+      </c>
+      <c r="C1077">
+        <v>1</v>
+      </c>
+      <c r="D1077" t="s">
+        <v>2803</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:5">
+      <c r="A1078" t="str">
+        <f t="shared" si="245"/>
+        <v>9F06</v>
+      </c>
+      <c r="B1078" t="str">
+        <f>_xlfn.XLOOKUP(C1078,'table of items'!C:C,'table of items'!D:D)</f>
+        <v>F301</v>
+      </c>
+      <c r="C1078" t="s">
+        <v>1474</v>
+      </c>
+      <c r="D1078" t="s">
+        <v>2803</v>
+      </c>
+      <c r="E1078">
+        <f>COUNTIF(C:C,"="&amp;C1078)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:5">
+      <c r="A1079" t="str">
+        <f t="shared" si="245"/>
+        <v>9F08</v>
+      </c>
+      <c r="B1079" t="str">
+        <f t="shared" ref="B1079" si="261">RIGHT(DEC2HEX(C1079,4),2)&amp;LEFT(DEC2HEX(C1079,4),2)</f>
+        <v>0100</v>
+      </c>
+      <c r="C1079">
+        <v>1</v>
+      </c>
+      <c r="D1079" t="s">
+        <v>2803</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:5">
+      <c r="A1080" t="str">
+        <f t="shared" si="245"/>
+        <v>9F0A</v>
+      </c>
+      <c r="B1080" t="str">
+        <f>_xlfn.XLOOKUP(C1080,'table of items'!C:C,'table of items'!D:D)</f>
+        <v>0A00</v>
+      </c>
+      <c r="C1080" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1080" t="s">
+        <v>2803</v>
+      </c>
+      <c r="E1080">
+        <f>COUNTIF(C:C,"="&amp;C1080)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:5">
+      <c r="A1081" t="str">
+        <f t="shared" si="245"/>
+        <v>9F0C</v>
+      </c>
+      <c r="B1081" t="str">
+        <f t="shared" ref="B1081" si="262">RIGHT(DEC2HEX(C1081,4),2)&amp;LEFT(DEC2HEX(C1081,4),2)</f>
+        <v>0100</v>
+      </c>
+      <c r="C1081">
+        <v>1</v>
+      </c>
+      <c r="D1081" t="s">
+        <v>2803</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:5">
+      <c r="A1082" t="str">
+        <f t="shared" ref="A1082:A1083" si="263">DEC2HEX(HEX2DEC(A1081)+LEN(B1081)/2,4)</f>
+        <v>9F0E</v>
+      </c>
+      <c r="B1082" t="str">
+        <f>_xlfn.XLOOKUP(C1082,'table of items'!C:C,'table of items'!D:D)</f>
+        <v>7E00</v>
+      </c>
+      <c r="C1082" t="s">
+        <v>3874</v>
+      </c>
+      <c r="D1082" t="s">
+        <v>2803</v>
+      </c>
+      <c r="E1082">
+        <f>COUNTIF(C:C,"="&amp;C1082)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:5">
+      <c r="A1083" t="str">
+        <f t="shared" si="263"/>
+        <v>9F10</v>
+      </c>
+      <c r="B1083" t="str">
+        <f t="shared" ref="B1083" si="264">RIGHT(DEC2HEX(C1083,4),2)&amp;LEFT(DEC2HEX(C1083,4),2)</f>
+        <v>0F00</v>
+      </c>
+      <c r="C1083">
+        <v>15</v>
+      </c>
+      <c r="D1083" t="s">
+        <v>2803</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C579:C594">
-    <sortCondition ref="C579:C594"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G899:G915">
+    <sortCondition ref="G899:G915"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -73549,7 +74257,7 @@
         <v>2549</v>
       </c>
       <c r="C878" t="s">
-        <v>341</v>
+        <v>3953</v>
       </c>
       <c r="D878" t="s">
         <v>2550</v>
@@ -73647,7 +74355,7 @@
         <v>2569</v>
       </c>
       <c r="C885" t="s">
-        <v>341</v>
+        <v>3946</v>
       </c>
       <c r="D885" t="s">
         <v>2570</v>
@@ -73661,7 +74369,7 @@
         <v>2571</v>
       </c>
       <c r="C886" t="s">
-        <v>341</v>
+        <v>3947</v>
       </c>
       <c r="D886" t="s">
         <v>2572</v>
@@ -73675,7 +74383,7 @@
         <v>2573</v>
       </c>
       <c r="C887" t="s">
-        <v>341</v>
+        <v>3949</v>
       </c>
       <c r="D887" t="s">
         <v>2574</v>
@@ -73689,7 +74397,7 @@
         <v>2575</v>
       </c>
       <c r="C888" t="s">
-        <v>341</v>
+        <v>3948</v>
       </c>
       <c r="D888" t="s">
         <v>2576</v>
@@ -73703,7 +74411,7 @@
         <v>2577</v>
       </c>
       <c r="C889" t="s">
-        <v>341</v>
+        <v>3950</v>
       </c>
       <c r="D889" t="s">
         <v>2578</v>
@@ -73717,7 +74425,7 @@
         <v>2579</v>
       </c>
       <c r="C890" t="s">
-        <v>341</v>
+        <v>3951</v>
       </c>
       <c r="D890" t="s">
         <v>2580</v>
@@ -73731,7 +74439,7 @@
         <v>2581</v>
       </c>
       <c r="C891" t="s">
-        <v>341</v>
+        <v>3952</v>
       </c>
       <c r="D891" t="s">
         <v>2582</v>
@@ -73745,7 +74453,7 @@
         <v>2583</v>
       </c>
       <c r="C892" t="s">
-        <v>341</v>
+        <v>3954</v>
       </c>
       <c r="D892" t="s">
         <v>2584</v>
@@ -73759,7 +74467,7 @@
         <v>2585</v>
       </c>
       <c r="C893" t="s">
-        <v>341</v>
+        <v>3955</v>
       </c>
       <c r="D893" t="s">
         <v>2586</v>
@@ -73773,7 +74481,7 @@
         <v>2587</v>
       </c>
       <c r="C894" t="s">
-        <v>341</v>
+        <v>3956</v>
       </c>
       <c r="D894" t="s">
         <v>2588</v>
@@ -73787,7 +74495,7 @@
         <v>2589</v>
       </c>
       <c r="C895" t="s">
-        <v>341</v>
+        <v>3957</v>
       </c>
       <c r="D895" t="s">
         <v>2590</v>
@@ -73801,7 +74509,7 @@
         <v>2591</v>
       </c>
       <c r="C896" t="s">
-        <v>341</v>
+        <v>3958</v>
       </c>
       <c r="D896" t="s">
         <v>2592</v>
@@ -73815,7 +74523,7 @@
         <v>2593</v>
       </c>
       <c r="C897" t="s">
-        <v>341</v>
+        <v>3959</v>
       </c>
       <c r="D897" t="s">
         <v>2594</v>
@@ -73829,7 +74537,7 @@
         <v>2595</v>
       </c>
       <c r="C898" t="s">
-        <v>341</v>
+        <v>3960</v>
       </c>
       <c r="D898" t="s">
         <v>2596</v>
@@ -73843,7 +74551,7 @@
         <v>2597</v>
       </c>
       <c r="C899" t="s">
-        <v>341</v>
+        <v>3961</v>
       </c>
       <c r="D899" t="s">
         <v>2598</v>
@@ -73857,7 +74565,7 @@
         <v>2599</v>
       </c>
       <c r="C900" t="s">
-        <v>341</v>
+        <v>3962</v>
       </c>
       <c r="D900" t="s">
         <v>2600</v>
@@ -73871,7 +74579,7 @@
         <v>2601</v>
       </c>
       <c r="C901" t="s">
-        <v>341</v>
+        <v>3963</v>
       </c>
       <c r="D901" t="s">
         <v>2602</v>
@@ -73885,7 +74593,7 @@
         <v>2603</v>
       </c>
       <c r="C902" t="s">
-        <v>341</v>
+        <v>3964</v>
       </c>
       <c r="D902" t="s">
         <v>2604</v>
@@ -75033,7 +75741,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1E21244-392A-4A73-9E9C-73FFA22F5FD4}">
-  <dimension ref="A1:AQ155"/>
+  <dimension ref="A1:AQ191"/>
   <sheetFormatPr defaultRowHeight="14.15"/>
   <sheetData>
     <row r="1" spans="1:43">
@@ -75333,7 +76041,7 @@
         <v>Bug Memory</v>
       </c>
       <c r="AP2" t="str" cm="1">
-        <f t="array" ref="AP2:AP155">_xlfn._xlws.FILTER(Edited!$C:$C,Edited!$D:$D=Sheet1!AP$1)</f>
+        <f t="array" ref="AP2:AP191">_xlfn._xlws.FILTER(Edited!$C:$C,Edited!$D:$D=Sheet1!AP$1)</f>
         <v>Abomasite</v>
       </c>
       <c r="AQ2" t="str" cm="1">
@@ -77240,7 +77948,7 @@
         <v>Poison Memory</v>
       </c>
       <c r="AP26" t="str">
-        <v>Beedrillite</v>
+        <v>Barbaricite</v>
       </c>
       <c r="AQ26" t="str">
         <v>Luxury Ball</v>
@@ -77322,7 +78030,7 @@
         <v>Psychic Memory</v>
       </c>
       <c r="AP28" t="str">
-        <v>Blastoisinite</v>
+        <v>Beedrillite</v>
       </c>
       <c r="AQ28" t="str">
         <v>Master Ball</v>
@@ -77398,7 +78106,7 @@
         <v>Rock Memory</v>
       </c>
       <c r="AP30" t="str">
-        <v>Blazikenite</v>
+        <v>Blastoisinite</v>
       </c>
       <c r="AQ30" t="str">
         <v>Moon Ball</v>
@@ -77468,7 +78176,7 @@
         <v>Steel Memory</v>
       </c>
       <c r="AP32" t="str">
-        <v>Butterfrinite</v>
+        <v>Blazikenite</v>
       </c>
       <c r="AQ32" t="str">
         <v>Nest Ball</v>
@@ -77538,7 +78246,7 @@
         <v>Water Memory</v>
       </c>
       <c r="AP34" t="str">
-        <v>Cameruptite</v>
+        <v>Butterfrinite</v>
       </c>
       <c r="AQ34" t="str">
         <v>Park Ball</v>
@@ -77608,7 +78316,7 @@
         <v>Draco Plate</v>
       </c>
       <c r="AP36" t="str">
-        <v>Chandelurite</v>
+        <v>Cameruptite</v>
       </c>
       <c r="AQ36" t="str">
         <v>Quick Ball</v>
@@ -77666,7 +78374,7 @@
         <v>Dread Plate</v>
       </c>
       <c r="AP38" t="str">
-        <v>Charizardite X</v>
+        <v>Chandelurite</v>
       </c>
       <c r="AQ38" t="str">
         <v>Safari Ball</v>
@@ -77709,7 +78417,7 @@
         <v>Earth Plate</v>
       </c>
       <c r="AP40" t="str">
-        <v>Charizardite Y</v>
+        <v>Charizardite X</v>
       </c>
       <c r="AQ40" t="str">
         <v>Sport Ball</v>
@@ -77746,7 +78454,7 @@
         <v>Fist Plate</v>
       </c>
       <c r="AP42" t="str">
-        <v>Cherriminite</v>
+        <v>Charizardite Y</v>
       </c>
       <c r="AQ42" t="str">
         <v>Timer Ball</v>
@@ -77780,7 +78488,7 @@
         <v>Flame Plate</v>
       </c>
       <c r="AP44" t="str">
-        <v>Chesnaughtite</v>
+        <v>Cherriminite</v>
       </c>
       <c r="AQ44" t="str">
         <v>Solar Sail</v>
@@ -77814,7 +78522,7 @@
         <v>Icicle Plate</v>
       </c>
       <c r="AP46" t="str">
-        <v>Chimechite</v>
+        <v>Chesnaughtite</v>
       </c>
     </row>
     <row r="47" spans="22:43">
@@ -77842,7 +78550,7 @@
         <v>Insect Plate</v>
       </c>
       <c r="AP48" t="str">
-        <v>Clefablite</v>
+        <v>Chimechite</v>
       </c>
     </row>
     <row r="49" spans="27:42">
@@ -77870,7 +78578,7 @@
         <v>Iron Plate</v>
       </c>
       <c r="AP50" t="str">
-        <v>Delphoxite</v>
+        <v>Clefablite</v>
       </c>
     </row>
     <row r="51" spans="27:42">
@@ -77898,7 +78606,7 @@
         <v>Meadow Plate</v>
       </c>
       <c r="AP52" t="str">
-        <v>Dragoninite</v>
+        <v>Crabominite</v>
       </c>
     </row>
     <row r="53" spans="27:42">
@@ -77926,7 +78634,7 @@
         <v>Mind Plate</v>
       </c>
       <c r="AP54" t="str">
-        <v>Feraligite</v>
+        <v>Delphoxite</v>
       </c>
     </row>
     <row r="55" spans="27:42">
@@ -77940,7 +78648,7 @@
         <v>6</v>
       </c>
       <c r="AP55">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="56" spans="27:42">
@@ -77948,13 +78656,13 @@
         <v>Chilan Berry</v>
       </c>
       <c r="AM56" t="str">
-        <v>Squirtilium Z</v>
+        <v>Squirtilium U</v>
       </c>
       <c r="AO56" t="str">
         <v>Pixie Plate</v>
       </c>
       <c r="AP56" t="str">
-        <v>Flygonite</v>
+        <v>Dragalgite</v>
       </c>
     </row>
     <row r="57" spans="27:42">
@@ -77982,7 +78690,7 @@
         <v>Sky Plate</v>
       </c>
       <c r="AP58" t="str">
-        <v>Froslassite</v>
+        <v>Dragoninite</v>
       </c>
     </row>
     <row r="59" spans="27:42">
@@ -78010,7 +78718,7 @@
         <v>Splash Plate</v>
       </c>
       <c r="AP60" t="str">
-        <v>Galladite</v>
+        <v>Drampanite</v>
       </c>
     </row>
     <row r="61" spans="27:42">
@@ -78038,7 +78746,7 @@
         <v>Spooky Plate</v>
       </c>
       <c r="AP62" t="str">
-        <v>Garbodorite</v>
+        <v>Eelektrossite</v>
       </c>
     </row>
     <row r="63" spans="27:42">
@@ -78052,7 +78760,7 @@
         <v>6</v>
       </c>
       <c r="AP63">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="64" spans="27:42">
@@ -78066,7 +78774,7 @@
         <v>Stone Plate</v>
       </c>
       <c r="AP64" t="str">
-        <v>Garchompite</v>
+        <v>Emboarite</v>
       </c>
     </row>
     <row r="65" spans="27:42">
@@ -78091,7 +78799,7 @@
         <v>Toxic Plate</v>
       </c>
       <c r="AP66" t="str">
-        <v>Gardevoirite</v>
+        <v>Excadrite</v>
       </c>
     </row>
     <row r="67" spans="27:42">
@@ -78113,7 +78821,7 @@
         <v>Zap Plate</v>
       </c>
       <c r="AP68" t="str">
-        <v>Gengarite</v>
+        <v>Feraligite</v>
       </c>
     </row>
     <row r="69" spans="27:42">
@@ -78132,7 +78840,7 @@
         <v>Kee Berry</v>
       </c>
       <c r="AP70" t="str">
-        <v>Glalitite</v>
+        <v>Flygonite</v>
       </c>
     </row>
     <row r="71" spans="27:42">
@@ -78145,7 +78853,7 @@
     </row>
     <row r="72" spans="27:42">
       <c r="AP72" t="str">
-        <v>Golurkite</v>
+        <v>Froslassite</v>
       </c>
     </row>
     <row r="73" spans="27:42">
@@ -78155,7 +78863,7 @@
     </row>
     <row r="74" spans="27:42">
       <c r="AP74" t="str">
-        <v>Gyaradosite</v>
+        <v>Galladite</v>
       </c>
     </row>
     <row r="75" spans="27:42">
@@ -78165,7 +78873,7 @@
     </row>
     <row r="76" spans="27:42">
       <c r="AP76" t="str">
-        <v>Heracronite</v>
+        <v>Garbodorite</v>
       </c>
     </row>
     <row r="77" spans="27:42">
@@ -78175,7 +78883,7 @@
     </row>
     <row r="78" spans="27:42">
       <c r="AP78" t="str">
-        <v>Houndoominite</v>
+        <v>Garchompite</v>
       </c>
     </row>
     <row r="79" spans="27:42">
@@ -78185,7 +78893,7 @@
     </row>
     <row r="80" spans="27:42">
       <c r="AP80" t="str">
-        <v>Kangaskhanite</v>
+        <v>Gardevoirite</v>
       </c>
     </row>
     <row r="81" spans="42:42">
@@ -78195,7 +78903,7 @@
     </row>
     <row r="82" spans="42:42">
       <c r="AP82" t="str">
-        <v>Kinglerite</v>
+        <v>Gengarite</v>
       </c>
     </row>
     <row r="83" spans="42:42">
@@ -78205,7 +78913,7 @@
     </row>
     <row r="84" spans="42:42">
       <c r="AP84" t="str">
-        <v>Laprasite</v>
+        <v>Glalitite</v>
       </c>
     </row>
     <row r="85" spans="42:42">
@@ -78215,7 +78923,7 @@
     </row>
     <row r="86" spans="42:42">
       <c r="AP86" t="str">
-        <v>Latiasite</v>
+        <v>Golurkite</v>
       </c>
     </row>
     <row r="87" spans="42:42">
@@ -78225,7 +78933,7 @@
     </row>
     <row r="88" spans="42:42">
       <c r="AP88" t="str">
-        <v>Latiosite</v>
+        <v>Gumshoosinite</v>
       </c>
     </row>
     <row r="89" spans="42:42">
@@ -78235,7 +78943,7 @@
     </row>
     <row r="90" spans="42:42">
       <c r="AP90" t="str">
-        <v>Lopunnite</v>
+        <v>Gyaradosite</v>
       </c>
     </row>
     <row r="91" spans="42:42">
@@ -78245,7 +78953,7 @@
     </row>
     <row r="92" spans="42:42">
       <c r="AP92" t="str">
-        <v>Lucarionite</v>
+        <v>Hawluchanite</v>
       </c>
     </row>
     <row r="93" spans="42:42">
@@ -78255,7 +78963,7 @@
     </row>
     <row r="94" spans="42:42">
       <c r="AP94" t="str">
-        <v>Lurantinite</v>
+        <v>Heracronite</v>
       </c>
     </row>
     <row r="95" spans="42:42">
@@ -78265,7 +78973,7 @@
     </row>
     <row r="96" spans="42:42">
       <c r="AP96" t="str">
-        <v>Machampinite</v>
+        <v>Houndoominite</v>
       </c>
     </row>
     <row r="97" spans="42:42">
@@ -78275,7 +78983,7 @@
     </row>
     <row r="98" spans="42:42">
       <c r="AP98" t="str">
-        <v>Magearnite</v>
+        <v>Kangaskhanite</v>
       </c>
     </row>
     <row r="99" spans="42:42">
@@ -78285,7 +78993,7 @@
     </row>
     <row r="100" spans="42:42">
       <c r="AP100" t="str">
-        <v>Manectite</v>
+        <v>Kinglerite</v>
       </c>
     </row>
     <row r="101" spans="42:42">
@@ -78295,7 +79003,7 @@
     </row>
     <row r="102" spans="42:42">
       <c r="AP102" t="str">
-        <v>Mawilite</v>
+        <v>Laprasite</v>
       </c>
     </row>
     <row r="103" spans="42:42">
@@ -78305,7 +79013,7 @@
     </row>
     <row r="104" spans="42:42">
       <c r="AP104" t="str">
-        <v>Medichamite</v>
+        <v>Latiasite</v>
       </c>
     </row>
     <row r="105" spans="42:42">
@@ -78315,7 +79023,7 @@
     </row>
     <row r="106" spans="42:42">
       <c r="AP106" t="str">
-        <v>Meganiumite</v>
+        <v>Latiosite</v>
       </c>
     </row>
     <row r="107" spans="42:42">
@@ -78325,7 +79033,7 @@
     </row>
     <row r="108" spans="42:42">
       <c r="AP108" t="str">
-        <v>Metagrossite</v>
+        <v>Lopunnite</v>
       </c>
     </row>
     <row r="109" spans="42:42">
@@ -78335,7 +79043,7 @@
     </row>
     <row r="110" spans="42:42">
       <c r="AP110" t="str">
-        <v>Mewtwonite X</v>
+        <v>Lucarionite</v>
       </c>
     </row>
     <row r="111" spans="42:42">
@@ -78345,7 +79053,7 @@
     </row>
     <row r="112" spans="42:42">
       <c r="AP112" t="str">
-        <v>Mewtwonite Y</v>
+        <v>Lurantinite</v>
       </c>
     </row>
     <row r="113" spans="42:42">
@@ -78355,7 +79063,7 @@
     </row>
     <row r="114" spans="42:42">
       <c r="AP114" t="str">
-        <v>Pidgeotite</v>
+        <v>Machampinite</v>
       </c>
     </row>
     <row r="115" spans="42:42">
@@ -78365,7 +79073,7 @@
     </row>
     <row r="116" spans="42:42">
       <c r="AP116" t="str">
-        <v>Pinsirite</v>
+        <v>Magearnite</v>
       </c>
     </row>
     <row r="117" spans="42:42">
@@ -78375,7 +79083,7 @@
     </row>
     <row r="118" spans="42:42">
       <c r="AP118" t="str">
-        <v>Ribombinite</v>
+        <v>Malamarite</v>
       </c>
     </row>
     <row r="119" spans="42:42">
@@ -78385,7 +79093,7 @@
     </row>
     <row r="120" spans="42:42">
       <c r="AP120" t="str">
-        <v>Sablenite</v>
+        <v>Manectite</v>
       </c>
     </row>
     <row r="121" spans="42:42">
@@ -78395,7 +79103,7 @@
     </row>
     <row r="122" spans="42:42">
       <c r="AP122" t="str">
-        <v>Salamencite</v>
+        <v>Mawilite</v>
       </c>
     </row>
     <row r="123" spans="42:42">
@@ -78405,7 +79113,7 @@
     </row>
     <row r="124" spans="42:42">
       <c r="AP124" t="str">
-        <v>Salazzlite</v>
+        <v>Medichamite</v>
       </c>
     </row>
     <row r="125" spans="42:42">
@@ -78415,7 +79123,7 @@
     </row>
     <row r="126" spans="42:42">
       <c r="AP126" t="str">
-        <v>Sceptilite</v>
+        <v>Meowsticite</v>
       </c>
     </row>
     <row r="127" spans="42:42">
@@ -78425,7 +79133,7 @@
     </row>
     <row r="128" spans="42:42">
       <c r="AP128" t="str">
-        <v>Scizorite</v>
+        <v>Meganiumite</v>
       </c>
     </row>
     <row r="129" spans="42:42">
@@ -78435,7 +79143,7 @@
     </row>
     <row r="130" spans="42:42">
       <c r="AP130" t="str">
-        <v>Sharpedonite</v>
+        <v>Metagrossite</v>
       </c>
     </row>
     <row r="131" spans="42:42">
@@ -78445,7 +79153,7 @@
     </row>
     <row r="132" spans="42:42">
       <c r="AP132" t="str">
-        <v>Skarmorite</v>
+        <v>Mewtwonite X</v>
       </c>
     </row>
     <row r="133" spans="42:42">
@@ -78455,7 +79163,7 @@
     </row>
     <row r="134" spans="42:42">
       <c r="AP134" t="str">
-        <v>Slowbronite</v>
+        <v>Mewtwonite Y</v>
       </c>
     </row>
     <row r="135" spans="42:42">
@@ -78465,7 +79173,7 @@
     </row>
     <row r="136" spans="42:42">
       <c r="AP136" t="str">
-        <v>Snorlaxite</v>
+        <v>Pidgeotite</v>
       </c>
     </row>
     <row r="137" spans="42:42">
@@ -78475,7 +79183,7 @@
     </row>
     <row r="138" spans="42:42">
       <c r="AP138" t="str">
-        <v>Soul Dew</v>
+        <v>Pinsirite</v>
       </c>
     </row>
     <row r="139" spans="42:42">
@@ -78485,7 +79193,7 @@
     </row>
     <row r="140" spans="42:42">
       <c r="AP140" t="str">
-        <v>Steelixite</v>
+        <v>Pyroarite</v>
       </c>
     </row>
     <row r="141" spans="42:42">
@@ -78495,7 +79203,7 @@
     </row>
     <row r="142" spans="42:42">
       <c r="AP142" t="str">
-        <v>Swampertite</v>
+        <v>Raichunite X</v>
       </c>
     </row>
     <row r="143" spans="42:42">
@@ -78505,7 +79213,7 @@
     </row>
     <row r="144" spans="42:42">
       <c r="AP144" t="str">
-        <v>Togekissite</v>
+        <v>Raichunite Y</v>
       </c>
     </row>
     <row r="145" spans="42:42">
@@ -78515,7 +79223,7 @@
     </row>
     <row r="146" spans="42:42">
       <c r="AP146" t="str">
-        <v>Tyranitarite</v>
+        <v>Ribombinite</v>
       </c>
     </row>
     <row r="147" spans="42:42">
@@ -78525,7 +79233,7 @@
     </row>
     <row r="148" spans="42:42">
       <c r="AP148" t="str">
-        <v>Tyrantrumite</v>
+        <v>Sablenite</v>
       </c>
     </row>
     <row r="149" spans="42:42">
@@ -78535,7 +79243,7 @@
     </row>
     <row r="150" spans="42:42">
       <c r="AP150" t="str">
-        <v>Venusaurite</v>
+        <v>Salamencite</v>
       </c>
     </row>
     <row r="151" spans="42:42">
@@ -78545,7 +79253,7 @@
     </row>
     <row r="152" spans="42:42">
       <c r="AP152" t="str">
-        <v>Victreebelite</v>
+        <v>Salazzlite</v>
       </c>
     </row>
     <row r="153" spans="42:42">
@@ -78555,11 +79263,191 @@
     </row>
     <row r="154" spans="42:42">
       <c r="AP154" t="str">
-        <v>Vikavoltinite</v>
+        <v>Sceptilite</v>
       </c>
     </row>
     <row r="155" spans="42:42">
       <c r="AP155">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="156" spans="42:42">
+      <c r="AP156" t="str">
+        <v>Scizorite</v>
+      </c>
+    </row>
+    <row r="157" spans="42:42">
+      <c r="AP157">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="158" spans="42:42">
+      <c r="AP158" t="str">
+        <v>Scolipite</v>
+      </c>
+    </row>
+    <row r="159" spans="42:42">
+      <c r="AP159">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="160" spans="42:42">
+      <c r="AP160" t="str">
+        <v>Scraftinite</v>
+      </c>
+    </row>
+    <row r="161" spans="42:42">
+      <c r="AP161">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="162" spans="42:42">
+      <c r="AP162" t="str">
+        <v>Sharpedonite</v>
+      </c>
+    </row>
+    <row r="163" spans="42:42">
+      <c r="AP163">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="164" spans="42:42">
+      <c r="AP164" t="str">
+        <v>Skarmorite</v>
+      </c>
+    </row>
+    <row r="165" spans="42:42">
+      <c r="AP165">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="166" spans="42:42">
+      <c r="AP166" t="str">
+        <v>Slowbronite</v>
+      </c>
+    </row>
+    <row r="167" spans="42:42">
+      <c r="AP167">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="168" spans="42:42">
+      <c r="AP168" t="str">
+        <v>Snorlaxite</v>
+      </c>
+    </row>
+    <row r="169" spans="42:42">
+      <c r="AP169">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="170" spans="42:42">
+      <c r="AP170" t="str">
+        <v>Soul Dew</v>
+      </c>
+    </row>
+    <row r="171" spans="42:42">
+      <c r="AP171">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="172" spans="42:42">
+      <c r="AP172" t="str">
+        <v>Staraptite</v>
+      </c>
+    </row>
+    <row r="173" spans="42:42">
+      <c r="AP173">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="174" spans="42:42">
+      <c r="AP174" t="str">
+        <v>Starminite</v>
+      </c>
+    </row>
+    <row r="175" spans="42:42">
+      <c r="AP175">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="176" spans="42:42">
+      <c r="AP176" t="str">
+        <v>Steelixite</v>
+      </c>
+    </row>
+    <row r="177" spans="42:42">
+      <c r="AP177">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="178" spans="42:42">
+      <c r="AP178" t="str">
+        <v>Swampertite</v>
+      </c>
+    </row>
+    <row r="179" spans="42:42">
+      <c r="AP179">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="180" spans="42:42">
+      <c r="AP180" t="str">
+        <v>Togekissite</v>
+      </c>
+    </row>
+    <row r="181" spans="42:42">
+      <c r="AP181">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="182" spans="42:42">
+      <c r="AP182" t="str">
+        <v>Tyranitarite</v>
+      </c>
+    </row>
+    <row r="183" spans="42:42">
+      <c r="AP183">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="184" spans="42:42">
+      <c r="AP184" t="str">
+        <v>Tyrantrumite</v>
+      </c>
+    </row>
+    <row r="185" spans="42:42">
+      <c r="AP185">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="186" spans="42:42">
+      <c r="AP186" t="str">
+        <v>Venusaurite</v>
+      </c>
+    </row>
+    <row r="187" spans="42:42">
+      <c r="AP187">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="188" spans="42:42">
+      <c r="AP188" t="str">
+        <v>Victreebelite</v>
+      </c>
+    </row>
+    <row r="189" spans="42:42">
+      <c r="AP189">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="190" spans="42:42">
+      <c r="AP190" t="str">
+        <v>Vikavoltinite</v>
+      </c>
+    </row>
+    <row r="191" spans="42:42">
+      <c r="AP191">
         <v>20</v>
       </c>
     </row>
